--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -1121,19 +1121,19 @@
         <v>7900</v>
       </c>
       <c r="E12" s="3">
-        <v>11800</v>
+        <v>11900</v>
       </c>
       <c r="F12" s="3">
         <v>16000</v>
       </c>
       <c r="G12" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="H12" s="3">
         <v>8200</v>
       </c>
       <c r="I12" s="3">
-        <v>12100</v>
+        <v>12200</v>
       </c>
       <c r="J12" s="3">
         <v>11400</v>
@@ -1529,8 +1529,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>4</v>
+      <c r="D17" s="3">
+        <v>12200</v>
       </c>
       <c r="E17" s="3">
         <v>10700</v>
@@ -1542,13 +1542,13 @@
         <v>8400</v>
       </c>
       <c r="H17" s="3">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="I17" s="3">
         <v>1200</v>
       </c>
       <c r="J17" s="3">
-        <v>16100</v>
+        <v>16200</v>
       </c>
       <c r="K17" s="3">
         <v>14100</v>
@@ -1624,8 +1624,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-12100</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>4</v>
@@ -1754,8 +1754,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>4000</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1849,8 +1849,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-8000</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>4</v>
@@ -1944,8 +1944,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>4</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -2039,14 +2039,14 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>4</v>
+      <c r="D23" s="3">
+        <v>-8100</v>
       </c>
       <c r="E23" s="3">
         <v>-8900</v>
       </c>
       <c r="F23" s="3">
-        <v>-12000</v>
+        <v>-12100</v>
       </c>
       <c r="G23" s="3">
         <v>-8700</v>
@@ -2324,14 +2324,14 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>4</v>
+      <c r="D26" s="3">
+        <v>-8100</v>
       </c>
       <c r="E26" s="3">
         <v>-8900</v>
       </c>
       <c r="F26" s="3">
-        <v>-12000</v>
+        <v>-12100</v>
       </c>
       <c r="G26" s="3">
         <v>-8700</v>
@@ -2419,14 +2419,14 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>4</v>
+      <c r="D27" s="3">
+        <v>-8100</v>
       </c>
       <c r="E27" s="3">
         <v>-8900</v>
       </c>
       <c r="F27" s="3">
-        <v>-12000</v>
+        <v>-12100</v>
       </c>
       <c r="G27" s="3">
         <v>-8700</v>
@@ -2894,8 +2894,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-4000</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -2989,14 +2989,14 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>4</v>
+      <c r="D33" s="3">
+        <v>-8100</v>
       </c>
       <c r="E33" s="3">
         <v>-8900</v>
       </c>
       <c r="F33" s="3">
-        <v>-12000</v>
+        <v>-12100</v>
       </c>
       <c r="G33" s="3">
         <v>-8700</v>
@@ -3179,14 +3179,14 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>4</v>
+      <c r="D35" s="3">
+        <v>-8100</v>
       </c>
       <c r="E35" s="3">
         <v>-8900</v>
       </c>
       <c r="F35" s="3">
-        <v>-12000</v>
+        <v>-12100</v>
       </c>
       <c r="G35" s="3">
         <v>-8700</v>
@@ -3445,7 +3445,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23500</v>
+        <v>14800</v>
       </c>
       <c r="E41" s="3">
         <v>6100</v>
@@ -3454,16 +3454,16 @@
         <v>2300</v>
       </c>
       <c r="G41" s="3">
-        <v>17600</v>
+        <v>17700</v>
       </c>
       <c r="H41" s="3">
-        <v>19500</v>
+        <v>19600</v>
       </c>
       <c r="I41" s="3">
-        <v>16700</v>
+        <v>16800</v>
       </c>
       <c r="J41" s="3">
-        <v>34800</v>
+        <v>34900</v>
       </c>
       <c r="K41" s="3">
         <v>14800</v>
@@ -3540,25 +3540,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>100900</v>
+        <v>110000</v>
       </c>
       <c r="E42" s="3">
-        <v>104900</v>
+        <v>105200</v>
       </c>
       <c r="F42" s="3">
-        <v>71800</v>
+        <v>72100</v>
       </c>
       <c r="G42" s="3">
-        <v>71100</v>
+        <v>71300</v>
       </c>
       <c r="H42" s="3">
-        <v>88500</v>
+        <v>88800</v>
       </c>
       <c r="I42" s="3">
-        <v>92300</v>
+        <v>92600</v>
       </c>
       <c r="J42" s="3">
-        <v>62900</v>
+        <v>63100</v>
       </c>
       <c r="K42" s="3">
         <v>75600</v>
@@ -3650,7 +3650,7 @@
         <v>1700</v>
       </c>
       <c r="I43" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="J43" s="3">
         <v>1300</v>
@@ -3825,7 +3825,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="E45" s="3">
         <v>7000</v>
@@ -3920,25 +3920,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>138400</v>
+        <v>138800</v>
       </c>
       <c r="E46" s="3">
-        <v>121800</v>
+        <v>122100</v>
       </c>
       <c r="F46" s="3">
-        <v>82900</v>
+        <v>83100</v>
       </c>
       <c r="G46" s="3">
-        <v>105700</v>
+        <v>106000</v>
       </c>
       <c r="H46" s="3">
-        <v>118000</v>
+        <v>118300</v>
       </c>
       <c r="I46" s="3">
-        <v>121700</v>
+        <v>122000</v>
       </c>
       <c r="J46" s="3">
-        <v>112500</v>
+        <v>112800</v>
       </c>
       <c r="K46" s="3">
         <v>103700</v>
@@ -4021,10 +4021,10 @@
         <v>20600</v>
       </c>
       <c r="F47" s="3">
-        <v>8600</v>
+        <v>8700</v>
       </c>
       <c r="G47" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="H47" s="3">
         <v>300</v>
@@ -4680,25 +4680,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>140500</v>
+        <v>140900</v>
       </c>
       <c r="E54" s="3">
-        <v>144300</v>
+        <v>144700</v>
       </c>
       <c r="F54" s="3">
-        <v>93600</v>
+        <v>93900</v>
       </c>
       <c r="G54" s="3">
-        <v>111100</v>
+        <v>111400</v>
       </c>
       <c r="H54" s="3">
-        <v>120600</v>
+        <v>120900</v>
       </c>
       <c r="I54" s="3">
-        <v>124400</v>
+        <v>124700</v>
       </c>
       <c r="J54" s="3">
-        <v>124900</v>
+        <v>125200</v>
       </c>
       <c r="K54" s="3">
         <v>135700</v>
@@ -4848,7 +4848,7 @@
         <v>6500</v>
       </c>
       <c r="E57" s="3">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="F57" s="3">
         <v>5000</v>
@@ -5053,7 +5053,7 @@
         <v>3300</v>
       </c>
       <c r="J59" s="3">
-        <v>9800</v>
+        <v>9900</v>
       </c>
       <c r="K59" s="3">
         <v>10600</v>
@@ -5139,7 +5139,7 @@
         <v>7400</v>
       </c>
       <c r="G60" s="3">
-        <v>14100</v>
+        <v>14200</v>
       </c>
       <c r="H60" s="3">
         <v>11500</v>
@@ -5703,13 +5703,13 @@
         <v>12500</v>
       </c>
       <c r="E66" s="3">
-        <v>9000</v>
+        <v>9100</v>
       </c>
       <c r="F66" s="3">
         <v>8400</v>
       </c>
       <c r="G66" s="3">
-        <v>15200</v>
+        <v>15300</v>
       </c>
       <c r="H66" s="3">
         <v>12700</v>
@@ -6210,25 +6210,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-250200</v>
+        <v>-250900</v>
       </c>
       <c r="E72" s="3">
-        <v>-242900</v>
+        <v>-243600</v>
       </c>
       <c r="F72" s="3">
-        <v>-235100</v>
+        <v>-235800</v>
       </c>
       <c r="G72" s="3">
-        <v>-224400</v>
+        <v>-225000</v>
       </c>
       <c r="H72" s="3">
-        <v>-216200</v>
+        <v>-216800</v>
       </c>
       <c r="I72" s="3">
-        <v>-208600</v>
+        <v>-209200</v>
       </c>
       <c r="J72" s="3">
-        <v>-211400</v>
+        <v>-212000</v>
       </c>
       <c r="K72" s="3">
         <v>-198800</v>
@@ -6590,25 +6590,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>128000</v>
+        <v>128400</v>
       </c>
       <c r="E76" s="3">
-        <v>135200</v>
+        <v>135600</v>
       </c>
       <c r="F76" s="3">
-        <v>85300</v>
+        <v>85500</v>
       </c>
       <c r="G76" s="3">
-        <v>95900</v>
+        <v>96100</v>
       </c>
       <c r="H76" s="3">
-        <v>107900</v>
+        <v>108200</v>
       </c>
       <c r="I76" s="3">
-        <v>110800</v>
+        <v>111100</v>
       </c>
       <c r="J76" s="3">
-        <v>103200</v>
+        <v>103500</v>
       </c>
       <c r="K76" s="3">
         <v>114100</v>
@@ -6879,14 +6879,14 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>4</v>
+      <c r="D81" s="3">
+        <v>-8100</v>
       </c>
       <c r="E81" s="3">
         <v>-8900</v>
       </c>
       <c r="F81" s="3">
-        <v>-12000</v>
+        <v>-12100</v>
       </c>
       <c r="G81" s="3">
         <v>-8700</v>
@@ -7583,7 +7583,7 @@
         <v>-5700</v>
       </c>
       <c r="E89" s="3">
-        <v>-12100</v>
+        <v>-12200</v>
       </c>
       <c r="F89" s="3">
         <v>-11400</v>
@@ -8010,10 +8010,10 @@
         <v>5400</v>
       </c>
       <c r="I94" s="3">
-        <v>-15100</v>
+        <v>-15200</v>
       </c>
       <c r="J94" s="3">
-        <v>28700</v>
+        <v>28800</v>
       </c>
       <c r="K94" s="3">
         <v>-36500</v>
@@ -8508,7 +8508,7 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
-        <v>57700</v>
+        <v>57800</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -8694,11 +8694,11 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>4</v>
+      <c r="D102" s="3">
+        <v>2400</v>
       </c>
       <c r="E102" s="3">
-        <v>18900</v>
+        <v>19000</v>
       </c>
       <c r="F102" s="3">
         <v>-15400</v>
@@ -8710,10 +8710,10 @@
         <v>2800</v>
       </c>
       <c r="I102" s="3">
-        <v>-26800</v>
+        <v>-26900</v>
       </c>
       <c r="J102" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="K102" s="3">
         <v>-47400</v>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,156 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
@@ -818,11 +825,11 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -887,19 +894,25 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
+      <c r="F9" s="3">
+        <v>300</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>4</v>
@@ -982,20 +995,26 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-200</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1077,8 +1096,14 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1121,94 +1148,100 @@
         <v>7900</v>
       </c>
       <c r="E12" s="3">
-        <v>11900</v>
+        <v>8700</v>
       </c>
       <c r="F12" s="3">
-        <v>16000</v>
+        <v>7900</v>
       </c>
       <c r="G12" s="3">
-        <v>9100</v>
+        <v>11800</v>
       </c>
       <c r="H12" s="3">
-        <v>8200</v>
+        <v>15900</v>
       </c>
       <c r="I12" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K12" s="3">
         <v>12200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>11400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>11000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>10100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>12000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>5800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>5400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>8000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>8000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>12800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>16400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>23800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>9200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>10700</v>
-      </c>
-      <c r="X12" s="3">
-        <v>6000</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>5500</v>
       </c>
       <c r="Z12" s="3">
         <v>6000</v>
       </c>
       <c r="AA12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AC12" s="3">
         <v>7100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>2900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>3500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>2800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>6200</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>1200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1397,8 +1436,14 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,114 +1575,122 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12200</v>
+        <v>13500</v>
       </c>
       <c r="E17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>12100</v>
+      </c>
+      <c r="G17" s="3">
         <v>10700</v>
       </c>
-      <c r="F17" s="3">
-        <v>11500</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>11400</v>
+      </c>
+      <c r="I17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>16200</v>
+      </c>
+      <c r="M17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="N17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="O17" s="3">
+        <v>14800</v>
+      </c>
+      <c r="P17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
-        <v>9400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="Q17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="R17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="S17" s="3">
+        <v>10500</v>
+      </c>
+      <c r="T17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="U17" s="3">
         <v>16200</v>
       </c>
-      <c r="K17" s="3">
-        <v>14100</v>
-      </c>
-      <c r="L17" s="3">
-        <v>13700</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="V17" s="3">
+        <v>19300</v>
+      </c>
+      <c r="W17" s="3">
+        <v>31900</v>
+      </c>
+      <c r="X17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Y17" s="3">
         <v>14800</v>
       </c>
-      <c r="N17" s="3">
-        <v>8400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>8200</v>
-      </c>
-      <c r="P17" s="3">
-        <v>6700</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>10500</v>
-      </c>
-      <c r="R17" s="3">
-        <v>10700</v>
-      </c>
-      <c r="S17" s="3">
-        <v>16200</v>
-      </c>
-      <c r="T17" s="3">
-        <v>19300</v>
-      </c>
-      <c r="U17" s="3">
-        <v>31900</v>
-      </c>
-      <c r="V17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="W17" s="3">
-        <v>14800</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>9300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>8900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>9200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>10600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>8100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>1800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-12000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>4</v>
@@ -1645,77 +1704,83 @@
       <c r="J18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M18" s="3">
         <v>-14100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-13700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-14800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-8400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-10500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-10700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-16200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-19300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-31900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-13100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-14800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,20 +1814,22 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F20" s="3">
         <v>4000</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1775,88 +1842,94 @@
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>6300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-7900</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>4</v>
@@ -1870,77 +1943,83 @@
       <c r="J21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3">
         <v>-13500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-15500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-6300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-10800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-8800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-15700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-17700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-29000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-11600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-12100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1977,11 +2056,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
@@ -1989,11 +2068,11 @@
       <c r="R22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2034,103 +2113,115 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-8900</v>
       </c>
-      <c r="F23" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-8700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-15200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-13700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-13000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-15600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-9000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-15900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-17800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-29500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-11800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-12200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2224,8 +2315,14 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-8100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I26" s="3">
         <v>-8700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-15200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-13700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-13000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-15600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-8800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-15900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-17800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-29500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-12200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-8100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I27" s="3">
         <v>-8700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-15200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-13700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-13000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-15600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-8800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-10900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-15900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-17800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-29500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-11800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-12200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,20 +3022,26 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4000</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
@@ -2915,172 +3054,184 @@
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>2600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-8100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I33" s="3">
         <v>-8700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-15200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-13700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-13000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-15600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-8800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-10900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-15900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-17800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-29500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-11800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-12200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-8100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I35" s="3">
         <v>-8700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-15200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-13700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-13000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-15600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-8800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-10900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-15900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-17800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-29500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-11800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-12200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,175 +3610,183 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>14700</v>
+      </c>
+      <c r="G41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I41" s="3">
+        <v>17600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="K41" s="3">
+        <v>16800</v>
+      </c>
+      <c r="L41" s="3">
+        <v>34900</v>
+      </c>
+      <c r="M41" s="3">
         <v>14800</v>
       </c>
-      <c r="E41" s="3">
-        <v>6100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>17700</v>
-      </c>
-      <c r="H41" s="3">
-        <v>19600</v>
-      </c>
-      <c r="I41" s="3">
-        <v>16800</v>
-      </c>
-      <c r="J41" s="3">
-        <v>34900</v>
-      </c>
-      <c r="K41" s="3">
-        <v>14800</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>12600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>46100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>63600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>7100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>26600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>62400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>171400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>126500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>138300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>24800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>28400</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>110000</v>
+        <v>83300</v>
       </c>
       <c r="E42" s="3">
-        <v>105200</v>
+        <v>89300</v>
       </c>
       <c r="F42" s="3">
-        <v>72100</v>
+        <v>109300</v>
       </c>
       <c r="G42" s="3">
-        <v>71300</v>
+        <v>104500</v>
       </c>
       <c r="H42" s="3">
-        <v>88800</v>
+        <v>71600</v>
       </c>
       <c r="I42" s="3">
+        <v>70800</v>
+      </c>
+      <c r="J42" s="3">
+        <v>88200</v>
+      </c>
+      <c r="K42" s="3">
         <v>92600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>63100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>75600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>88500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>123000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>137100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>79400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>52900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>103200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>115900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>32500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>27700</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="3">
         <v>49300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>38900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>60000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3617,11 +3796,11 @@
       <c r="AC42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -3629,53 +3808,59 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F43" s="3">
         <v>3700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3688,11 +3873,11 @@
       <c r="U43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3724,23 +3909,29 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F44" s="3">
         <v>1800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3753,11 +3944,11 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3819,233 +4010,251 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8500</v>
+        <v>6300</v>
       </c>
       <c r="E45" s="3">
-        <v>7000</v>
+        <v>4400</v>
       </c>
       <c r="F45" s="3">
-        <v>6500</v>
+        <v>8400</v>
       </c>
       <c r="G45" s="3">
-        <v>15400</v>
+        <v>6900</v>
       </c>
       <c r="H45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>15300</v>
+      </c>
+      <c r="J45" s="3">
         <v>8200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>13600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>11900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>4400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>3600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>100200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>136800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>104100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>126600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>121600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>9800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>138800</v>
+        <v>111300</v>
       </c>
       <c r="E46" s="3">
-        <v>122100</v>
+        <v>118300</v>
       </c>
       <c r="F46" s="3">
-        <v>83100</v>
+        <v>137800</v>
       </c>
       <c r="G46" s="3">
-        <v>106000</v>
+        <v>121300</v>
       </c>
       <c r="H46" s="3">
-        <v>118300</v>
+        <v>82600</v>
       </c>
       <c r="I46" s="3">
+        <v>105300</v>
+      </c>
+      <c r="J46" s="3">
+        <v>117500</v>
+      </c>
+      <c r="K46" s="3">
         <v>122000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>112800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>103700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>108000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>139900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>153900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>86100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>103000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>110800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>121200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>138900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>169900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>167700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>183000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>187100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>124200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>181200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>127300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>139100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>26700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>29600</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
-        <v>20600</v>
-      </c>
-      <c r="F47" s="3">
-        <v>8700</v>
-      </c>
       <c r="G47" s="3">
-        <v>3200</v>
+        <v>20500</v>
       </c>
       <c r="H47" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I47" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J47" s="3">
         <v>300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>10100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>29500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>28800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>300</v>
-      </c>
-      <c r="N47" s="3">
-        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
@@ -4072,31 +4281,31 @@
         <v>300</v>
       </c>
       <c r="W47" s="3">
+        <v>300</v>
+      </c>
+      <c r="X47" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y47" s="3">
         <v>200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>57400</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
         <v>100</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>4</v>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>4</v>
@@ -4104,103 +4313,115 @@
       <c r="AG47" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI47" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="E48" s="3">
         <v>1500</v>
       </c>
       <c r="F48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L48" s="3">
         <v>1700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="M48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="N48" s="3">
         <v>1900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="O48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P48" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="U48" s="3">
+        <v>1600</v>
+      </c>
+      <c r="V48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="W48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X48" s="3">
         <v>1700</v>
       </c>
-      <c r="K48" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>900</v>
-      </c>
-      <c r="O48" s="3">
-        <v>1000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1900</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4214,10 +4435,10 @@
         <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I49" s="3">
         <v>200</v>
@@ -4226,10 +4447,10 @@
         <v>200</v>
       </c>
       <c r="K49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M49" s="3">
         <v>300</v>
@@ -4241,52 +4462,52 @@
         <v>300</v>
       </c>
       <c r="P49" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>300</v>
+      </c>
+      <c r="R49" s="3">
         <v>400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>500</v>
-      </c>
-      <c r="S49" s="3">
-        <v>500</v>
-      </c>
-      <c r="T49" s="3">
-        <v>600</v>
       </c>
       <c r="U49" s="3">
         <v>500</v>
       </c>
       <c r="V49" s="3">
+        <v>600</v>
+      </c>
+      <c r="W49" s="3">
+        <v>500</v>
+      </c>
+      <c r="X49" s="3">
         <v>400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>300</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
         <v>100</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>0</v>
-      </c>
       <c r="AB49" s="3">
         <v>0</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>4</v>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>4</v>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,8 +4717,14 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4502,10 +4741,10 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
         <v>400</v>
@@ -4529,37 +4768,37 @@
         <v>400</v>
       </c>
       <c r="Q52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>500</v>
       </c>
       <c r="T52" s="3">
+        <v>500</v>
+      </c>
+      <c r="U52" s="3">
+        <v>500</v>
+      </c>
+      <c r="V52" s="3">
         <v>600</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
+      <c r="AA52" s="3">
+        <v>0</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
@@ -4567,11 +4806,11 @@
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>0</v>
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -4579,8 +4818,14 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>140900</v>
+        <v>115700</v>
       </c>
       <c r="E54" s="3">
-        <v>144700</v>
+        <v>129900</v>
       </c>
       <c r="F54" s="3">
-        <v>93900</v>
+        <v>139900</v>
       </c>
       <c r="G54" s="3">
-        <v>111400</v>
+        <v>143700</v>
       </c>
       <c r="H54" s="3">
-        <v>120900</v>
+        <v>93300</v>
       </c>
       <c r="I54" s="3">
+        <v>110700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>120100</v>
+      </c>
+      <c r="K54" s="3">
         <v>124700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>125200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>135700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>139300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>142900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>155800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>88000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>105200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>113300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>123800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>141900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>173400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>170500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>185400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>188300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>182300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>181800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>127600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>139400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>26900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>29800</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +5098,111 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>12900</v>
+      </c>
+      <c r="F57" s="3">
         <v>6500</v>
       </c>
-      <c r="E57" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H57" s="3">
         <v>5000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5400</v>
       </c>
-      <c r="H57" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K57" s="3">
         <v>8600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>10300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>9300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>9400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>7500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>8200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>10400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>11600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>11400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>14500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>20300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>14300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>8400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>2800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2800</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4973,46 +5240,46 @@
         <v>400</v>
       </c>
       <c r="O58" s="3">
+        <v>400</v>
+      </c>
+      <c r="P58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>600</v>
-      </c>
-      <c r="R58" s="3">
-        <v>600</v>
       </c>
       <c r="S58" s="3">
         <v>600</v>
       </c>
       <c r="T58" s="3">
+        <v>600</v>
+      </c>
+      <c r="U58" s="3">
+        <v>600</v>
+      </c>
+      <c r="V58" s="3">
         <v>400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>300</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5029,236 +5296,254 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F59" s="3">
         <v>4700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>8300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>9900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>10600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1000</v>
       </c>
       <c r="Q59" s="3">
         <v>1500</v>
       </c>
       <c r="R59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>5100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>11600</v>
+        <v>12500</v>
       </c>
       <c r="E60" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11500</v>
+      </c>
+      <c r="G60" s="3">
         <v>8100</v>
       </c>
-      <c r="F60" s="3">
-        <v>7400</v>
-      </c>
-      <c r="G60" s="3">
-        <v>14200</v>
-      </c>
       <c r="H60" s="3">
-        <v>11500</v>
+        <v>7300</v>
       </c>
       <c r="I60" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>11400</v>
+      </c>
+      <c r="K60" s="3">
         <v>12300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>20600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>20300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>14000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>10100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>13600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>12800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>16400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>21700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>15700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>10100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>9200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>6600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>4100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>4600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>5300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>3000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>3000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>800</v>
+      </c>
+      <c r="F61" s="3">
         <v>900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>200</v>
-      </c>
-      <c r="O61" s="3">
-        <v>300</v>
       </c>
       <c r="P61" s="3">
         <v>200</v>
@@ -5267,26 +5552,26 @@
         <v>300</v>
       </c>
       <c r="R61" s="3">
+        <v>200</v>
+      </c>
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
+        <v>300</v>
+      </c>
+      <c r="U61" s="3">
         <v>400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>600</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5297,25 +5582,31 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>64400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>63500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5334,29 +5625,29 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
@@ -5364,14 +5655,14 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>100</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V62" s="3">
         <v>100</v>
@@ -5386,10 +5677,10 @@
         <v>100</v>
       </c>
       <c r="Z62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5397,11 +5688,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>4</v>
@@ -5409,8 +5700,14 @@
       <c r="AG62" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12500</v>
+        <v>13300</v>
       </c>
       <c r="E66" s="3">
-        <v>9100</v>
+        <v>19000</v>
       </c>
       <c r="F66" s="3">
+        <v>12400</v>
+      </c>
+      <c r="G66" s="3">
+        <v>9000</v>
+      </c>
+      <c r="H66" s="3">
         <v>8400</v>
       </c>
-      <c r="G66" s="3">
-        <v>15300</v>
-      </c>
-      <c r="H66" s="3">
-        <v>12700</v>
-      </c>
       <c r="I66" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K66" s="3">
         <v>13600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>21700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>21500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>15200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>12100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>8900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>13100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>16800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>22500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>16500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>10800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>4200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>4600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>67500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>66500</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-250900</v>
+        <v>-274400</v>
       </c>
       <c r="E72" s="3">
-        <v>-243600</v>
+        <v>-265900</v>
       </c>
       <c r="F72" s="3">
-        <v>-235800</v>
+        <v>-249200</v>
       </c>
       <c r="G72" s="3">
-        <v>-225000</v>
+        <v>-241900</v>
       </c>
       <c r="H72" s="3">
-        <v>-216800</v>
+        <v>-234200</v>
       </c>
       <c r="I72" s="3">
+        <v>-223500</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-215300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-209200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-212000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-198800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-184400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-169600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-155000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-141700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-138500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-137500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-127100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-127500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-118500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-98800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-84400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-74300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>172100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>174200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>119900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>130800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>128400</v>
+        <v>102400</v>
       </c>
       <c r="E76" s="3">
-        <v>135600</v>
+        <v>110900</v>
       </c>
       <c r="F76" s="3">
-        <v>85500</v>
+        <v>127500</v>
       </c>
       <c r="G76" s="3">
-        <v>96100</v>
+        <v>134700</v>
       </c>
       <c r="H76" s="3">
-        <v>108200</v>
+        <v>84900</v>
       </c>
       <c r="I76" s="3">
+        <v>95500</v>
+      </c>
+      <c r="J76" s="3">
+        <v>107500</v>
+      </c>
+      <c r="K76" s="3">
         <v>111100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>103500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>114100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>124100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>130800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>146900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>77700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>93100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>99400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>110800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>125100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>150900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>154000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>174600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>179100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>175600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>177600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>123000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>134000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-8100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="I81" s="3">
         <v>-8700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-15200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-13700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-13000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-15600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-8800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-10900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-15900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-17800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-29500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-11800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-12200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,16 +7399,18 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -7058,25 +7455,25 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
       </c>
       <c r="W83" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
       </c>
       <c r="Y83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -7096,11 +7493,17 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-5700</v>
       </c>
-      <c r="E89" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-11400</v>
       </c>
-      <c r="G89" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-13600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-14000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-12700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-10700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-8300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-11000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-9700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-8400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-11500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-18900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-32000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-10200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-10000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +8143,10 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7719,14 +8160,14 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -7746,61 +8187,67 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-200</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
       <c r="Z91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8442,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F94" s="3">
         <v>8000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-26400</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-15200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>28800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-36500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>6200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>3200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-7800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>33100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>27100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-24200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>19800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>7100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-107500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-100</v>
       </c>
       <c r="AB94" s="3">
         <v>-100</v>
       </c>
       <c r="AC94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8984,14 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8508,175 +8999,181 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
-        <v>57800</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>57400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>2400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>65400</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
       <c r="P100" s="3">
+        <v>65400</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R100" s="3">
         <v>9300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>54000</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>120400</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>36200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>36300</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>2000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>2600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>1400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>1800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>5800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
@@ -8686,102 +9183,114 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="F102" s="3">
         <v>2400</v>
       </c>
-      <c r="E102" s="3">
-        <v>19000</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-15400</v>
-      </c>
       <c r="G102" s="3">
+        <v>18800</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-26900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>15100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-47400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>55800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-18800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>32600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-13100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>7100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-23100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-11200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-9800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-110400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>44800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>113500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>30300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>34700</v>
       </c>
-      <c r="AG102" s="3" t="s">
+      <c r="AI102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,151 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -811,11 +815,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>4</v>
       </c>
@@ -831,8 +835,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -900,22 +904,25 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>400</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
-      </c>
-      <c r="E9" s="3">
-        <v>300</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>4</v>
+      <c r="G9" s="3">
+        <v>300</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>4</v>
@@ -1001,8 +1008,11 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1010,14 +1020,14 @@
         <v>4</v>
       </c>
       <c r="E10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F10" s="3">
         <v>-300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-200</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,109 +1152,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>7900</v>
+        <v>11100</v>
       </c>
       <c r="E12" s="3">
-        <v>8700</v>
+        <v>8100</v>
       </c>
       <c r="F12" s="3">
-        <v>7900</v>
+        <v>8900</v>
       </c>
       <c r="G12" s="3">
-        <v>11800</v>
+        <v>8100</v>
       </c>
       <c r="H12" s="3">
-        <v>15900</v>
+        <v>12100</v>
       </c>
       <c r="I12" s="3">
-        <v>9000</v>
+        <v>16300</v>
       </c>
       <c r="J12" s="3">
+        <v>9200</v>
+      </c>
+      <c r="K12" s="3">
         <v>8100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>12200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5400</v>
-      </c>
-      <c r="S12" s="3">
-        <v>8000</v>
       </c>
       <c r="T12" s="3">
         <v>8000</v>
       </c>
       <c r="U12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="V12" s="3">
         <v>12800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>16400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>10700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>2900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>3500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>6200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,109 +1603,113 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13500</v>
+        <v>17100</v>
       </c>
       <c r="E17" s="3">
-        <v>14400</v>
+        <v>13900</v>
       </c>
       <c r="F17" s="3">
-        <v>12100</v>
+        <v>14700</v>
       </c>
       <c r="G17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>10900</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M17" s="3">
+        <v>16200</v>
+      </c>
+      <c r="N17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="O17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="P17" s="3">
+        <v>14800</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="R17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="S17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="T17" s="3">
+        <v>10500</v>
+      </c>
+      <c r="U17" s="3">
         <v>10700</v>
       </c>
-      <c r="H17" s="3">
-        <v>11400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>8300</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="V17" s="3">
+        <v>16200</v>
+      </c>
+      <c r="W17" s="3">
+        <v>19300</v>
+      </c>
+      <c r="X17" s="3">
+        <v>31900</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AA17" s="3">
         <v>9300</v>
       </c>
-      <c r="K17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>16200</v>
-      </c>
-      <c r="M17" s="3">
-        <v>14100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>13700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>14800</v>
-      </c>
-      <c r="P17" s="3">
-        <v>8400</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>8200</v>
-      </c>
-      <c r="R17" s="3">
-        <v>6700</v>
-      </c>
-      <c r="S17" s="3">
-        <v>10500</v>
-      </c>
-      <c r="T17" s="3">
-        <v>10700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>16200</v>
-      </c>
-      <c r="V17" s="3">
-        <v>19300</v>
-      </c>
-      <c r="W17" s="3">
-        <v>31900</v>
-      </c>
-      <c r="X17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>14800</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>9300</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1687,13 +1717,13 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
-        <v>-14400</v>
+        <v>-13900</v>
       </c>
       <c r="F18" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>4</v>
+        <v>-14700</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-12300</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>4</v>
@@ -1710,77 +1740,80 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="3">
         <v>-14100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-16200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-19300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-31900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-14800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1825,13 +1859,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>-2800</v>
+        <v>3200</v>
       </c>
       <c r="F20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>4</v>
+        <v>-2900</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4100</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>4</v>
@@ -1848,77 +1882,80 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-500</v>
       </c>
       <c r="S20" s="3">
         <v>-500</v>
       </c>
       <c r="T20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U20" s="3">
         <v>1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-900</v>
       </c>
       <c r="AE20" s="3">
         <v>-900</v>
       </c>
       <c r="AF20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1926,13 +1963,13 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>-17000</v>
+        <v>-10600</v>
       </c>
       <c r="F21" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
+        <v>-17500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-8100</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>4</v>
@@ -1949,77 +1986,80 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-13500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-15500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-8700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-17700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-29000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI21" s="3" t="s">
+      <c r="AJ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2062,8 +2102,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>4</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>4</v>
@@ -2074,8 +2114,8 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2119,109 +2159,115 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-10400</v>
+        <v>-15300</v>
       </c>
       <c r="E23" s="3">
-        <v>-17200</v>
+        <v>-10700</v>
       </c>
       <c r="F23" s="3">
-        <v>-8100</v>
+        <v>-17600</v>
       </c>
       <c r="G23" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="J23" s="3">
         <v>-8900</v>
       </c>
-      <c r="H23" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-17800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-29500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-10400</v>
+        <v>-15300</v>
       </c>
       <c r="E26" s="3">
-        <v>-17200</v>
+        <v>-10700</v>
       </c>
       <c r="F26" s="3">
-        <v>-8100</v>
+        <v>-17600</v>
       </c>
       <c r="G26" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-15900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-17800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-29500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-10400</v>
+        <v>-15300</v>
       </c>
       <c r="E27" s="3">
-        <v>-17200</v>
+        <v>-10700</v>
       </c>
       <c r="F27" s="3">
-        <v>-8100</v>
+        <v>-17600</v>
       </c>
       <c r="G27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="J27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-15900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-17800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-29500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3037,13 +3107,13 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>2800</v>
+        <v>-3200</v>
       </c>
       <c r="F32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>4</v>
+        <v>2900</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-4100</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>4</v>
@@ -3060,178 +3130,184 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
-      </c>
-      <c r="R32" s="3">
-        <v>500</v>
       </c>
       <c r="S32" s="3">
         <v>500</v>
       </c>
       <c r="T32" s="3">
+        <v>500</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2600</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>900</v>
       </c>
       <c r="AE32" s="3">
         <v>900</v>
       </c>
       <c r="AF32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-10400</v>
+        <v>-15300</v>
       </c>
       <c r="E33" s="3">
-        <v>-17200</v>
+        <v>-10700</v>
       </c>
       <c r="F33" s="3">
-        <v>-8100</v>
+        <v>-17600</v>
       </c>
       <c r="G33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="J33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-15900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-17800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-29500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-10400</v>
+        <v>-15300</v>
       </c>
       <c r="E35" s="3">
-        <v>-17200</v>
+        <v>-10700</v>
       </c>
       <c r="F35" s="3">
-        <v>-8100</v>
+        <v>-17600</v>
       </c>
       <c r="G35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="J35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-15900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-17800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-29500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,98 +3698,99 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7400</v>
+        <v>3200</v>
       </c>
       <c r="E41" s="3">
-        <v>8200</v>
+        <v>7500</v>
       </c>
       <c r="F41" s="3">
-        <v>14700</v>
+        <v>8400</v>
       </c>
       <c r="G41" s="3">
-        <v>6000</v>
+        <v>15100</v>
       </c>
       <c r="H41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I41" s="3">
         <v>2300</v>
       </c>
-      <c r="I41" s="3">
-        <v>17600</v>
-      </c>
       <c r="J41" s="3">
+        <v>18000</v>
+      </c>
+      <c r="K41" s="3">
         <v>19400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>63600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>26600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>62400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>171400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>126500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>138300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28400</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3713,83 +3800,86 @@
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>83300</v>
+        <v>79800</v>
       </c>
       <c r="E42" s="3">
-        <v>89300</v>
+        <v>85400</v>
       </c>
       <c r="F42" s="3">
-        <v>109300</v>
+        <v>91500</v>
       </c>
       <c r="G42" s="3">
-        <v>104500</v>
+        <v>112000</v>
       </c>
       <c r="H42" s="3">
-        <v>71600</v>
+        <v>107100</v>
       </c>
       <c r="I42" s="3">
-        <v>70800</v>
+        <v>73300</v>
       </c>
       <c r="J42" s="3">
+        <v>72600</v>
+      </c>
+      <c r="K42" s="3">
         <v>88200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>92600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>63100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>75600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>88500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>123000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>137100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>79400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>52900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>103200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>115900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>32500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>27700</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="3">
         <v>49300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>38900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>60000</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3802,8 +3892,8 @@
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -3814,55 +3904,58 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="E43" s="3">
-        <v>4100</v>
+        <v>2400</v>
       </c>
       <c r="F43" s="3">
-        <v>3700</v>
+        <v>4200</v>
       </c>
       <c r="G43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
-        <v>2300</v>
-      </c>
       <c r="I43" s="3">
-        <v>1500</v>
+        <v>2400</v>
       </c>
       <c r="J43" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K43" s="3">
         <v>1700</v>
       </c>
       <c r="L43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>900</v>
-      </c>
-      <c r="P43" s="3">
-        <v>1400</v>
       </c>
       <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>4</v>
+      <c r="R43" s="3">
+        <v>1400</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>4</v>
@@ -3879,8 +3972,8 @@
       <c r="W43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3915,26 +4008,29 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>11900</v>
+        <v>10700</v>
       </c>
       <c r="E44" s="3">
-        <v>12300</v>
+        <v>12200</v>
       </c>
       <c r="F44" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G44" s="3">
         <v>1800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3950,8 +4046,8 @@
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -4016,98 +4112,101 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6300</v>
+        <v>5400</v>
       </c>
       <c r="E45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>15700</v>
+      </c>
+      <c r="K45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L45" s="3">
+        <v>11000</v>
+      </c>
+      <c r="M45" s="3">
+        <v>13600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>11900</v>
+      </c>
+      <c r="O45" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P45" s="3">
         <v>4400</v>
       </c>
-      <c r="F45" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="Q45" s="3">
         <v>6900</v>
       </c>
-      <c r="H45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>15300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>8200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>11000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>13600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>11900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>4400</v>
-      </c>
-      <c r="P45" s="3">
-        <v>6900</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>136800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>104100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>126600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>121600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>9800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4117,98 +4216,101 @@
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>111300</v>
+        <v>101100</v>
       </c>
       <c r="E46" s="3">
-        <v>118300</v>
+        <v>114000</v>
       </c>
       <c r="F46" s="3">
-        <v>137800</v>
+        <v>121200</v>
       </c>
       <c r="G46" s="3">
-        <v>121300</v>
+        <v>141300</v>
       </c>
       <c r="H46" s="3">
-        <v>82600</v>
+        <v>124300</v>
       </c>
       <c r="I46" s="3">
-        <v>105300</v>
+        <v>84600</v>
       </c>
       <c r="J46" s="3">
+        <v>107900</v>
+      </c>
+      <c r="K46" s="3">
         <v>117500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>112800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>103700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>108000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>139900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>153900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>86100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>103000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>110800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>121200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>138900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>169900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>167700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>183000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>187100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>124200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>181200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>127300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>139100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>29600</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4218,46 +4320,49 @@
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2700</v>
+        <v>300</v>
       </c>
       <c r="E47" s="3">
-        <v>9800</v>
+        <v>2800</v>
       </c>
       <c r="F47" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G47" s="3">
         <v>300</v>
       </c>
-      <c r="G47" s="3">
-        <v>20500</v>
-      </c>
       <c r="H47" s="3">
-        <v>8600</v>
+        <v>21000</v>
       </c>
       <c r="I47" s="3">
-        <v>3100</v>
+        <v>8800</v>
       </c>
       <c r="J47" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="K47" s="3">
         <v>300</v>
       </c>
       <c r="L47" s="3">
+        <v>300</v>
+      </c>
+      <c r="M47" s="3">
         <v>10100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>28800</v>
-      </c>
-      <c r="O47" s="3">
-        <v>300</v>
       </c>
       <c r="P47" s="3">
         <v>300</v>
@@ -4287,28 +4392,28 @@
         <v>300</v>
       </c>
       <c r="Y47" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z47" s="3">
         <v>200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>57400</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
       <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>100</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
       <c r="AD47" s="3">
         <v>0</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>4</v>
+      <c r="AF47" s="3">
+        <v>0</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>4</v>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4340,77 +4448,77 @@
         <v>1600</v>
       </c>
       <c r="I48" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="J48" s="3">
         <v>1800</v>
       </c>
       <c r="K48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L48" s="3">
         <v>1900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1900</v>
       </c>
       <c r="W48" s="3">
         <v>1900</v>
       </c>
       <c r="X48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>700</v>
       </c>
       <c r="Z48" s="3">
         <v>700</v>
       </c>
       <c r="AA48" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB48" s="3">
         <v>500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>300</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>200</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
       </c>
       <c r="AE48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF48" s="3">
         <v>100</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4420,13 +4528,16 @@
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
@@ -4441,7 +4552,7 @@
         <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
         <v>200</v>
@@ -4453,7 +4564,7 @@
         <v>200</v>
       </c>
       <c r="M49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N49" s="3">
         <v>300</v>
@@ -4468,38 +4579,38 @@
         <v>300</v>
       </c>
       <c r="R49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S49" s="3">
         <v>400</v>
       </c>
       <c r="T49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U49" s="3">
         <v>500</v>
       </c>
       <c r="V49" s="3">
+        <v>500</v>
+      </c>
+      <c r="W49" s="3">
         <v>600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>300</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
       <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
         <v>100</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
@@ -4509,8 +4620,8 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>4</v>
+      <c r="AF49" s="3">
+        <v>0</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>4</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4747,7 +4867,7 @@
         <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>400</v>
@@ -4774,7 +4894,7 @@
         <v>400</v>
       </c>
       <c r="S52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T52" s="3">
         <v>500</v>
@@ -4783,25 +4903,25 @@
         <v>500</v>
       </c>
       <c r="V52" s="3">
+        <v>500</v>
+      </c>
+      <c r="W52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
@@ -4812,8 +4932,8 @@
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
+      <c r="AF52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,98 +5048,101 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>115700</v>
+        <v>103000</v>
       </c>
       <c r="E54" s="3">
-        <v>129900</v>
+        <v>118600</v>
       </c>
       <c r="F54" s="3">
-        <v>139900</v>
+        <v>133100</v>
       </c>
       <c r="G54" s="3">
-        <v>143700</v>
+        <v>143400</v>
       </c>
       <c r="H54" s="3">
-        <v>93300</v>
+        <v>147300</v>
       </c>
       <c r="I54" s="3">
-        <v>110700</v>
+        <v>95600</v>
       </c>
       <c r="J54" s="3">
+        <v>113400</v>
+      </c>
+      <c r="K54" s="3">
         <v>120100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>124700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>125200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>135700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>139300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>142900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>155800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>88000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>105200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>113300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>123800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>141900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>173400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>170500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>185400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>188300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>182300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>181800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>127600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>139400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>26900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29800</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,97 +5230,98 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>8600</v>
+      </c>
+      <c r="M57" s="3">
+        <v>10300</v>
+      </c>
+      <c r="N57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="O57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="P57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="R57" s="3">
         <v>8200</v>
       </c>
-      <c r="E57" s="3">
-        <v>12900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>5600</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="S57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="T57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="U57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="V57" s="3">
+        <v>14500</v>
+      </c>
+      <c r="W57" s="3">
+        <v>20300</v>
+      </c>
+      <c r="X57" s="3">
+        <v>14300</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="AD57" s="3">
         <v>5000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>8000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>8600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>10300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>9300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>12400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>9400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>7500</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>8200</v>
-      </c>
-      <c r="R57" s="3">
-        <v>10400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>11600</v>
-      </c>
-      <c r="T57" s="3">
-        <v>11400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>14500</v>
-      </c>
-      <c r="V57" s="3">
-        <v>20300</v>
-      </c>
-      <c r="W57" s="3">
-        <v>14300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>8400</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>7900</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>2400</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>3400</v>
-      </c>
-      <c r="AC57" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>2800</v>
       </c>
       <c r="AE57" s="3">
         <v>2800</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>4</v>
+      <c r="AF57" s="3">
+        <v>2800</v>
       </c>
       <c r="AG57" s="3" t="s">
         <v>4</v>
@@ -5201,8 +5332,11 @@
       <c r="AI57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5246,13 +5380,13 @@
         <v>400</v>
       </c>
       <c r="Q58" s="3">
+        <v>400</v>
+      </c>
+      <c r="R58" s="3">
         <v>300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>500</v>
-      </c>
-      <c r="S58" s="3">
-        <v>600</v>
       </c>
       <c r="T58" s="3">
         <v>600</v>
@@ -5261,17 +5395,17 @@
         <v>600</v>
       </c>
       <c r="V58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="W58" s="3">
         <v>400</v>
       </c>
       <c r="X58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y58" s="3">
         <v>300</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5281,8 +5415,8 @@
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5302,97 +5436,100 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3900</v>
+        <v>1400</v>
       </c>
       <c r="E59" s="3">
-        <v>4900</v>
+        <v>4000</v>
       </c>
       <c r="F59" s="3">
-        <v>4700</v>
+        <v>11400</v>
       </c>
       <c r="G59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2000</v>
       </c>
-      <c r="I59" s="3">
-        <v>8300</v>
-      </c>
       <c r="J59" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K59" s="3">
         <v>3000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>200</v>
       </c>
       <c r="AE59" s="3">
         <v>200</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
+      <c r="AF59" s="3">
+        <v>200</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>4</v>
@@ -5403,97 +5540,100 @@
       <c r="AI59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12500</v>
+        <v>11300</v>
       </c>
       <c r="E60" s="3">
-        <v>18200</v>
+        <v>12800</v>
       </c>
       <c r="F60" s="3">
-        <v>11500</v>
+        <v>18700</v>
       </c>
       <c r="G60" s="3">
-        <v>8100</v>
+        <v>11800</v>
       </c>
       <c r="H60" s="3">
-        <v>7300</v>
+        <v>8300</v>
       </c>
       <c r="I60" s="3">
-        <v>14100</v>
+        <v>7500</v>
       </c>
       <c r="J60" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K60" s="3">
         <v>11400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>6600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5300</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>3000</v>
       </c>
       <c r="AE60" s="3">
         <v>3000</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>4</v>
+      <c r="AF60" s="3">
+        <v>3000</v>
       </c>
       <c r="AG60" s="3" t="s">
         <v>4</v>
@@ -5504,13 +5644,16 @@
       <c r="AI60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E61" s="3">
         <v>800</v>
@@ -5522,59 +5665,59 @@
         <v>900</v>
       </c>
       <c r="H61" s="3">
+        <v>900</v>
+      </c>
+      <c r="I61" s="3">
         <v>1000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>200</v>
-      </c>
-      <c r="S61" s="3">
-        <v>300</v>
       </c>
       <c r="T61" s="3">
         <v>300</v>
       </c>
       <c r="U61" s="3">
+        <v>300</v>
+      </c>
+      <c r="V61" s="3">
         <v>400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>600</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5588,14 +5731,14 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>64400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>63500</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5605,8 +5748,11 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5631,14 +5777,14 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
@@ -5646,11 +5792,11 @@
       <c r="O62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
@@ -5661,11 +5807,11 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3">
         <v>100</v>
@@ -5683,7 +5829,7 @@
         <v>100</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5694,8 +5840,8 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>4</v>
+      <c r="AF62" s="3">
+        <v>0</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>4</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,98 +6164,101 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13300</v>
+        <v>12100</v>
       </c>
       <c r="E66" s="3">
-        <v>19000</v>
+        <v>13700</v>
       </c>
       <c r="F66" s="3">
-        <v>12400</v>
+        <v>19500</v>
       </c>
       <c r="G66" s="3">
-        <v>9000</v>
+        <v>12700</v>
       </c>
       <c r="H66" s="3">
-        <v>8400</v>
+        <v>9200</v>
       </c>
       <c r="I66" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="L66" s="3">
+        <v>13600</v>
+      </c>
+      <c r="M66" s="3">
+        <v>21700</v>
+      </c>
+      <c r="N66" s="3">
+        <v>21500</v>
+      </c>
+      <c r="O66" s="3">
         <v>15200</v>
       </c>
-      <c r="J66" s="3">
-        <v>12600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>13600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>21700</v>
-      </c>
-      <c r="M66" s="3">
-        <v>21500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>15200</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>67500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>66500</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6110,8 +6268,11 @@
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,98 +6722,101 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-274400</v>
+        <v>-295200</v>
       </c>
       <c r="E72" s="3">
-        <v>-265900</v>
+        <v>-281200</v>
       </c>
       <c r="F72" s="3">
-        <v>-249200</v>
+        <v>-272600</v>
       </c>
       <c r="G72" s="3">
-        <v>-241900</v>
+        <v>-255400</v>
       </c>
       <c r="H72" s="3">
-        <v>-234200</v>
+        <v>-248000</v>
       </c>
       <c r="I72" s="3">
-        <v>-223500</v>
+        <v>-240000</v>
       </c>
       <c r="J72" s="3">
+        <v>-229100</v>
+      </c>
+      <c r="K72" s="3">
         <v>-215300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-209200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-212000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-198800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-184400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-169600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-155000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-141700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-138500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-137500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-127100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-127500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-118500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-98800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-84400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-74300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>172100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>174200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>119900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>130800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,98 +7138,101 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>102400</v>
+        <v>91000</v>
       </c>
       <c r="E76" s="3">
-        <v>110900</v>
+        <v>105000</v>
       </c>
       <c r="F76" s="3">
-        <v>127500</v>
+        <v>113600</v>
       </c>
       <c r="G76" s="3">
-        <v>134700</v>
+        <v>130700</v>
       </c>
       <c r="H76" s="3">
-        <v>84900</v>
+        <v>138100</v>
       </c>
       <c r="I76" s="3">
-        <v>95500</v>
+        <v>87000</v>
       </c>
       <c r="J76" s="3">
+        <v>97900</v>
+      </c>
+      <c r="K76" s="3">
         <v>107500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>111100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>103500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>114100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>124100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>130800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>146900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>77700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>93100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>99400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>110800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>125100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>150900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>154000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>174600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>179100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>175600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>177600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>123000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>134000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7056,8 +7242,11 @@
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-10400</v>
+        <v>-15300</v>
       </c>
       <c r="E81" s="3">
-        <v>-17200</v>
+        <v>-10700</v>
       </c>
       <c r="F81" s="3">
-        <v>-8100</v>
+        <v>-17600</v>
       </c>
       <c r="G81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="J81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
-        <v>-12000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-8700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-15900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-17800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-29500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,13 +7599,14 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -7461,13 +7660,13 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>500</v>
-      </c>
-      <c r="X83" s="3">
-        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
@@ -7476,7 +7675,7 @@
         <v>100</v>
       </c>
       <c r="AA83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -7499,11 +7698,14 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-16100</v>
+        <v>-13400</v>
       </c>
       <c r="E89" s="3">
-        <v>-11800</v>
+        <v>-16500</v>
       </c>
       <c r="F89" s="3">
-        <v>-5700</v>
+        <v>-12000</v>
       </c>
       <c r="G89" s="3">
-        <v>-12100</v>
+        <v>-5800</v>
       </c>
       <c r="H89" s="3">
-        <v>-11400</v>
+        <v>-12400</v>
       </c>
       <c r="I89" s="3">
-        <v>-5600</v>
+        <v>-11600</v>
       </c>
       <c r="J89" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-18900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-32000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI89" s="3" t="s">
+      <c r="AJ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8365,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8166,11 +8387,11 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -8193,11 +8414,11 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -8205,25 +8426,25 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-900</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-300</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
       <c r="Z91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-100</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
@@ -8232,22 +8453,25 @@
         <v>-100</v>
       </c>
       <c r="AE91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI91" s="3" t="s">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,85 +8675,88 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>29100</v>
+        <v>6600</v>
       </c>
       <c r="E94" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F94" s="3">
         <v>3100</v>
       </c>
-      <c r="F94" s="3">
-        <v>8000</v>
-      </c>
       <c r="G94" s="3">
-        <v>-26300</v>
+        <v>8200</v>
       </c>
       <c r="H94" s="3">
-        <v>-3900</v>
+        <v>-26900</v>
       </c>
       <c r="I94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J94" s="3">
         <v>2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>5400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>28800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-36500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>6200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>3200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>33100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>27100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>19800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>7100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-100</v>
       </c>
       <c r="AC94" s="3">
         <v>-100</v>
@@ -8535,22 +8765,25 @@
         <v>-100</v>
       </c>
       <c r="AE94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI94" s="3" t="s">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9233,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9005,16 +9251,16 @@
         <v>-100</v>
       </c>
       <c r="G100" s="3">
-        <v>57400</v>
+        <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
+        <v>58900</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>-100</v>
@@ -9023,160 +9269,163 @@
         <v>-100</v>
       </c>
       <c r="M100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
       <c r="P100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>65400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-100</v>
       </c>
       <c r="U100" s="3">
         <v>-100</v>
       </c>
       <c r="V100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>54000</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>120400</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>1800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>36200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>36300</v>
       </c>
-      <c r="AI100" s="3" t="s">
+      <c r="AJ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
-        <v>-800</v>
-      </c>
       <c r="F101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
         <v>0</v>
       </c>
@@ -9189,108 +9438,114 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>13300</v>
+        <v>-6600</v>
       </c>
       <c r="E102" s="3">
-        <v>-9600</v>
+        <v>13700</v>
       </c>
       <c r="F102" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="G102" s="3">
         <v>2400</v>
       </c>
-      <c r="G102" s="3">
-        <v>18800</v>
-      </c>
       <c r="H102" s="3">
-        <v>-15300</v>
+        <v>19300</v>
       </c>
       <c r="I102" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-26900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-47400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>55800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-18800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-23100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-110400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>44800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>113500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>30300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>34700</v>
       </c>
-      <c r="AI102" s="3" t="s">
+      <c r="AJ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,160 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -818,11 +822,11 @@
         <v>0</v>
       </c>
       <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>4</v>
       </c>
@@ -838,8 +842,8 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
+      <c r="N8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
@@ -907,25 +911,28 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200</v>
-      </c>
-      <c r="F9" s="3">
-        <v>300</v>
       </c>
       <c r="G9" s="3">
         <v>300</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
+      <c r="H9" s="3">
+        <v>300</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>4</v>
@@ -1011,26 +1018,29 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
+      <c r="D10" s="3">
+        <v>200</v>
       </c>
       <c r="E10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F10" s="3">
         <v>-200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-200</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1115,8 +1125,11 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,112 +1166,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>11100</v>
+        <v>12400</v>
       </c>
       <c r="E12" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>11900</v>
+      </c>
+      <c r="J12" s="3">
+        <v>16000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L12" s="3">
         <v>8100</v>
       </c>
-      <c r="F12" s="3">
-        <v>8900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>8100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>12100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>16300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>9200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>8100</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>12200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5400</v>
-      </c>
-      <c r="T12" s="3">
-        <v>8000</v>
       </c>
       <c r="U12" s="3">
         <v>8000</v>
       </c>
       <c r="V12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="W12" s="3">
         <v>12800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>16400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>23800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>10700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>6000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>2900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>3500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,31 +1378,34 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>14800</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-5300</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-8400</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1465,31 +1485,34 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1569,8 +1592,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,135 +1630,139 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17100</v>
+        <v>17300</v>
       </c>
       <c r="E17" s="3">
-        <v>13900</v>
+        <v>16500</v>
       </c>
       <c r="F17" s="3">
-        <v>14700</v>
+        <v>13500</v>
       </c>
       <c r="G17" s="3">
-        <v>12400</v>
+        <v>-100</v>
       </c>
       <c r="H17" s="3">
-        <v>10900</v>
+        <v>12700</v>
       </c>
       <c r="I17" s="3">
-        <v>11700</v>
+        <v>16100</v>
       </c>
       <c r="J17" s="3">
+        <v>19900</v>
+      </c>
+      <c r="K17" s="3">
         <v>8500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>19300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>8100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-17100</v>
       </c>
       <c r="E18" s="3">
-        <v>-13900</v>
+        <v>-16500</v>
       </c>
       <c r="F18" s="3">
-        <v>-14700</v>
+        <v>-13500</v>
       </c>
       <c r="G18" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-19900</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>4</v>
@@ -1743,77 +1773,80 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3">
         <v>-14100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-16200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-19300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-31900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,31 +1883,32 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>3200</v>
       </c>
       <c r="E20" s="3">
-        <v>3200</v>
+        <v>-800</v>
       </c>
       <c r="F20" s="3">
-        <v>-2900</v>
+        <v>-2100</v>
       </c>
       <c r="G20" s="3">
         <v>4100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
@@ -1885,100 +1919,103 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-500</v>
       </c>
       <c r="T20" s="3">
         <v>-500</v>
       </c>
       <c r="U20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V20" s="3">
         <v>1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-900</v>
       </c>
       <c r="AF20" s="3">
         <v>-900</v>
       </c>
       <c r="AG20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-20200</v>
       </c>
       <c r="E21" s="3">
-        <v>-10600</v>
+        <v>-15600</v>
       </c>
       <c r="F21" s="3">
-        <v>-17500</v>
+        <v>-11300</v>
       </c>
       <c r="G21" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-4000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-20800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1989,77 +2026,80 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3">
         <v>-13500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-15500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-17700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-29000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ21" s="3" t="s">
+      <c r="AK21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2105,8 +2145,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>4</v>
@@ -2117,8 +2157,8 @@
       <c r="U22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2162,135 +2202,141 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-15300</v>
+        <v>-19500</v>
       </c>
       <c r="E23" s="3">
-        <v>-10700</v>
+        <v>-14800</v>
       </c>
       <c r="F23" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-17600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H23" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="I23" s="3">
-        <v>-12300</v>
+        <v>-9000</v>
       </c>
       <c r="J23" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-8900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-17800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2370,8 +2416,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-15300</v>
+        <v>-19500</v>
       </c>
       <c r="E26" s="3">
-        <v>-10700</v>
+        <v>-14800</v>
       </c>
       <c r="F26" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="G26" s="3">
         <v>-17600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H26" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="I26" s="3">
-        <v>-12300</v>
+        <v>-9000</v>
       </c>
       <c r="J26" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-8900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-15900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-17800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-15300</v>
+        <v>-19500</v>
       </c>
       <c r="E27" s="3">
-        <v>-10700</v>
+        <v>-14800</v>
       </c>
       <c r="F27" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="G27" s="3">
         <v>-17600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H27" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="I27" s="3">
-        <v>-12300</v>
+        <v>-9000</v>
       </c>
       <c r="J27" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-8900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-15900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-17800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2951,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,31 +3165,34 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>-3200</v>
       </c>
       <c r="E32" s="3">
-        <v>-3200</v>
+        <v>800</v>
       </c>
       <c r="F32" s="3">
-        <v>2900</v>
+        <v>2100</v>
       </c>
       <c r="G32" s="3">
         <v>-4100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
+      <c r="H32" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I32" s="3">
+        <v>600</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1000</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
@@ -3133,181 +3203,187 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
-      </c>
-      <c r="S32" s="3">
-        <v>500</v>
       </c>
       <c r="T32" s="3">
         <v>500</v>
       </c>
       <c r="U32" s="3">
+        <v>500</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2600</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>900</v>
       </c>
       <c r="AF32" s="3">
         <v>900</v>
       </c>
       <c r="AG32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH32" s="3">
         <v>1000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-15300</v>
+        <v>-19500</v>
       </c>
       <c r="E33" s="3">
-        <v>-10700</v>
+        <v>-14800</v>
       </c>
       <c r="F33" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="G33" s="3">
         <v>-17600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H33" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="I33" s="3">
-        <v>-12300</v>
+        <v>-9000</v>
       </c>
       <c r="J33" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-8900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-15900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-17800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-15300</v>
+        <v>-19500</v>
       </c>
       <c r="E35" s="3">
-        <v>-10700</v>
+        <v>-14800</v>
       </c>
       <c r="F35" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="G35" s="3">
         <v>-17600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H35" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="I35" s="3">
-        <v>-12300</v>
+        <v>-9000</v>
       </c>
       <c r="J35" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-8900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-15900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-17800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,101 +3785,102 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3200</v>
+        <v>29200</v>
       </c>
       <c r="E41" s="3">
-        <v>7500</v>
+        <v>20500</v>
       </c>
       <c r="F41" s="3">
+        <v>27100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>23000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>21300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K41" s="3">
+        <v>18000</v>
+      </c>
+      <c r="L41" s="3">
+        <v>19400</v>
+      </c>
+      <c r="M41" s="3">
+        <v>16800</v>
+      </c>
+      <c r="N41" s="3">
+        <v>34900</v>
+      </c>
+      <c r="O41" s="3">
+        <v>14800</v>
+      </c>
+      <c r="P41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>11500</v>
+      </c>
+      <c r="R41" s="3">
         <v>8400</v>
       </c>
-      <c r="G41" s="3">
-        <v>15100</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="S41" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T41" s="3">
+        <v>46100</v>
+      </c>
+      <c r="U41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="V41" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W41" s="3">
         <v>6200</v>
       </c>
-      <c r="I41" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>18000</v>
-      </c>
-      <c r="K41" s="3">
-        <v>19400</v>
-      </c>
-      <c r="L41" s="3">
-        <v>16800</v>
-      </c>
-      <c r="M41" s="3">
-        <v>34900</v>
-      </c>
-      <c r="N41" s="3">
-        <v>14800</v>
-      </c>
-      <c r="O41" s="3">
-        <v>12600</v>
-      </c>
-      <c r="P41" s="3">
-        <v>11500</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>8400</v>
-      </c>
-      <c r="R41" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S41" s="3">
-        <v>46100</v>
-      </c>
-      <c r="T41" s="3">
-        <v>4400</v>
-      </c>
-      <c r="U41" s="3">
-        <v>1700</v>
-      </c>
-      <c r="V41" s="3">
-        <v>6200</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>63600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>26600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>62400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>171400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>126500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>138300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28400</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3803,86 +3890,89 @@
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>79800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>85400</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>91500</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>112000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>107100</v>
+        <v>1200</v>
       </c>
       <c r="I42" s="3">
-        <v>73300</v>
+        <v>5700</v>
       </c>
       <c r="J42" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K42" s="3">
         <v>72600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>88200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>92600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>63100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>75600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>88500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>123000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>137100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>79400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>52900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>103200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>115900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>32500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>27700</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z42" s="3">
         <v>49300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>38900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>60000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3895,8 +3985,8 @@
       <c r="AF42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -3907,58 +3997,61 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2000</v>
+        <v>2600</v>
       </c>
       <c r="E43" s="3">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="F43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G43" s="3">
         <v>4200</v>
       </c>
-      <c r="G43" s="3">
-        <v>3800</v>
-      </c>
       <c r="H43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="I43" s="3">
-        <v>2400</v>
-      </c>
       <c r="J43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K43" s="3">
         <v>1600</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1700</v>
       </c>
       <c r="L43" s="3">
         <v>1700</v>
       </c>
       <c r="M43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>900</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1400</v>
       </c>
       <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>4</v>
+      <c r="S43" s="3">
+        <v>1400</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>4</v>
@@ -3975,8 +4068,8 @@
       <c r="X43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -4011,29 +4104,32 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10700</v>
+        <v>10800</v>
       </c>
       <c r="E44" s="3">
-        <v>12200</v>
+        <v>10300</v>
       </c>
       <c r="F44" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G44" s="3">
         <v>12600</v>
       </c>
-      <c r="G44" s="3">
-        <v>1800</v>
-      </c>
       <c r="H44" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4049,8 +4145,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4115,101 +4211,104 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5400</v>
+        <v>38600</v>
       </c>
       <c r="E45" s="3">
-        <v>6500</v>
+        <v>63800</v>
       </c>
       <c r="F45" s="3">
-        <v>4500</v>
+        <v>68200</v>
       </c>
       <c r="G45" s="3">
-        <v>8600</v>
+        <v>89800</v>
       </c>
       <c r="H45" s="3">
-        <v>7100</v>
+        <v>104700</v>
       </c>
       <c r="I45" s="3">
-        <v>6600</v>
+        <v>90500</v>
       </c>
       <c r="J45" s="3">
+        <v>74700</v>
+      </c>
+      <c r="K45" s="3">
         <v>15700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>136800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>104100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>126600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>121600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>9800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1200</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4219,101 +4318,104 @@
       <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>101100</v>
+        <v>82100</v>
       </c>
       <c r="E46" s="3">
-        <v>114000</v>
+        <v>97800</v>
       </c>
       <c r="F46" s="3">
+        <v>111100</v>
+      </c>
+      <c r="G46" s="3">
+        <v>121000</v>
+      </c>
+      <c r="H46" s="3">
+        <v>135000</v>
+      </c>
+      <c r="I46" s="3">
+        <v>122500</v>
+      </c>
+      <c r="J46" s="3">
+        <v>83000</v>
+      </c>
+      <c r="K46" s="3">
+        <v>107900</v>
+      </c>
+      <c r="L46" s="3">
+        <v>117500</v>
+      </c>
+      <c r="M46" s="3">
+        <v>122000</v>
+      </c>
+      <c r="N46" s="3">
+        <v>112800</v>
+      </c>
+      <c r="O46" s="3">
+        <v>103700</v>
+      </c>
+      <c r="P46" s="3">
+        <v>108000</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>139900</v>
+      </c>
+      <c r="R46" s="3">
+        <v>153900</v>
+      </c>
+      <c r="S46" s="3">
+        <v>86100</v>
+      </c>
+      <c r="T46" s="3">
+        <v>103000</v>
+      </c>
+      <c r="U46" s="3">
+        <v>110800</v>
+      </c>
+      <c r="V46" s="3">
         <v>121200</v>
       </c>
-      <c r="G46" s="3">
-        <v>141300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>124300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>84600</v>
-      </c>
-      <c r="J46" s="3">
-        <v>107900</v>
-      </c>
-      <c r="K46" s="3">
-        <v>117500</v>
-      </c>
-      <c r="L46" s="3">
-        <v>122000</v>
-      </c>
-      <c r="M46" s="3">
-        <v>112800</v>
-      </c>
-      <c r="N46" s="3">
-        <v>103700</v>
-      </c>
-      <c r="O46" s="3">
-        <v>108000</v>
-      </c>
-      <c r="P46" s="3">
-        <v>139900</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>153900</v>
-      </c>
-      <c r="R46" s="3">
-        <v>86100</v>
-      </c>
-      <c r="S46" s="3">
-        <v>103000</v>
-      </c>
-      <c r="T46" s="3">
-        <v>110800</v>
-      </c>
-      <c r="U46" s="3">
-        <v>121200</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>138900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>169900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>167700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>183000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>187100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>124200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>181200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>127300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>139100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>26700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>29600</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4323,49 +4425,52 @@
       <c r="AJ46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
-        <v>2800</v>
-      </c>
       <c r="F47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G47" s="3">
         <v>10000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>300</v>
       </c>
-      <c r="H47" s="3">
-        <v>21000</v>
-      </c>
       <c r="I47" s="3">
-        <v>8800</v>
+        <v>20700</v>
       </c>
       <c r="J47" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K47" s="3">
         <v>3200</v>
-      </c>
-      <c r="K47" s="3">
-        <v>300</v>
       </c>
       <c r="L47" s="3">
         <v>300</v>
       </c>
       <c r="M47" s="3">
+        <v>300</v>
+      </c>
+      <c r="N47" s="3">
         <v>10100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>28800</v>
-      </c>
-      <c r="P47" s="3">
-        <v>300</v>
       </c>
       <c r="Q47" s="3">
         <v>300</v>
@@ -4395,28 +4500,28 @@
         <v>300</v>
       </c>
       <c r="Z47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA47" s="3">
         <v>200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>57400</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>100</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
-      </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>4</v>
+      <c r="AG47" s="3">
+        <v>0</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>4</v>
@@ -4427,101 +4532,104 @@
       <c r="AJ47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F48" s="3">
         <v>1400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1500</v>
       </c>
       <c r="G48" s="3">
         <v>1500</v>
       </c>
       <c r="H48" s="3">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="I48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J48" s="3">
         <v>1700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1800</v>
       </c>
       <c r="K48" s="3">
         <v>1800</v>
       </c>
       <c r="L48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M48" s="3">
         <v>1900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1900</v>
       </c>
       <c r="X48" s="3">
         <v>1900</v>
       </c>
       <c r="Y48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1700</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>700</v>
       </c>
       <c r="AA48" s="3">
         <v>700</v>
       </c>
       <c r="AB48" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC48" s="3">
         <v>500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>300</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>200</v>
       </c>
       <c r="AE48" s="3">
         <v>200</v>
       </c>
       <c r="AF48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG48" s="3">
         <v>100</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4531,8 +4639,11 @@
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4540,13 +4651,13 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
         <v>100</v>
@@ -4555,7 +4666,7 @@
         <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -4567,7 +4678,7 @@
         <v>200</v>
       </c>
       <c r="N49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
@@ -4582,38 +4693,38 @@
         <v>300</v>
       </c>
       <c r="S49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T49" s="3">
         <v>400</v>
       </c>
       <c r="U49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V49" s="3">
         <v>500</v>
       </c>
       <c r="W49" s="3">
+        <v>500</v>
+      </c>
+      <c r="X49" s="3">
         <v>600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>300</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
-      </c>
       <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
         <v>100</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
       <c r="AD49" s="3">
         <v>0</v>
       </c>
@@ -4623,8 +4734,8 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>4</v>
+      <c r="AG49" s="3">
+        <v>0</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>4</v>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,16 +4960,19 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>300</v>
@@ -4870,7 +4990,7 @@
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>400</v>
@@ -4897,7 +5017,7 @@
         <v>400</v>
       </c>
       <c r="T52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U52" s="3">
         <v>500</v>
@@ -4906,25 +5026,25 @@
         <v>500</v>
       </c>
       <c r="W52" s="3">
+        <v>500</v>
+      </c>
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>4</v>
@@ -4935,8 +5055,8 @@
       <c r="AF52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH52" s="3">
         <v>0</v>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,101 +5174,104 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>103000</v>
+        <v>88900</v>
       </c>
       <c r="E54" s="3">
-        <v>118600</v>
+        <v>99700</v>
       </c>
       <c r="F54" s="3">
-        <v>133100</v>
+        <v>115500</v>
       </c>
       <c r="G54" s="3">
-        <v>143400</v>
+        <v>132900</v>
       </c>
       <c r="H54" s="3">
-        <v>147300</v>
+        <v>137100</v>
       </c>
       <c r="I54" s="3">
-        <v>95600</v>
+        <v>145200</v>
       </c>
       <c r="J54" s="3">
+        <v>93800</v>
+      </c>
+      <c r="K54" s="3">
         <v>113400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>124700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>125200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>135700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>139300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>142900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>155800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>88000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>105200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>113300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>123800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>141900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>173400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>170500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>185400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>188300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>182300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>181800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>127600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>139400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>26900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29800</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5155,8 +5281,11 @@
       <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,100 +5361,101 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9500</v>
+        <v>13100</v>
       </c>
       <c r="E57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="G57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L57" s="3">
+        <v>8000</v>
+      </c>
+      <c r="M57" s="3">
+        <v>8600</v>
+      </c>
+      <c r="N57" s="3">
+        <v>10300</v>
+      </c>
+      <c r="O57" s="3">
+        <v>9300</v>
+      </c>
+      <c r="P57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>9400</v>
+      </c>
+      <c r="R57" s="3">
+        <v>7500</v>
+      </c>
+      <c r="S57" s="3">
+        <v>8200</v>
+      </c>
+      <c r="T57" s="3">
+        <v>10400</v>
+      </c>
+      <c r="U57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="V57" s="3">
+        <v>11400</v>
+      </c>
+      <c r="W57" s="3">
+        <v>14500</v>
+      </c>
+      <c r="X57" s="3">
+        <v>20300</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>14300</v>
+      </c>
+      <c r="Z57" s="3">
         <v>8400</v>
       </c>
-      <c r="F57" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>6600</v>
-      </c>
-      <c r="H57" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>5500</v>
-      </c>
-      <c r="K57" s="3">
-        <v>8000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>8600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>10300</v>
-      </c>
-      <c r="N57" s="3">
-        <v>9300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>12400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>9400</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>7500</v>
-      </c>
-      <c r="R57" s="3">
-        <v>8200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>10400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>11600</v>
-      </c>
-      <c r="U57" s="3">
-        <v>11400</v>
-      </c>
-      <c r="V57" s="3">
-        <v>14500</v>
-      </c>
-      <c r="W57" s="3">
-        <v>20300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>14300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>8400</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>2800</v>
       </c>
       <c r="AF57" s="3">
         <v>2800</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>4</v>
+      <c r="AG57" s="3">
+        <v>2800</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>4</v>
@@ -5335,8 +5466,11 @@
       <c r="AJ57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5383,13 +5517,13 @@
         <v>400</v>
       </c>
       <c r="R58" s="3">
+        <v>400</v>
+      </c>
+      <c r="S58" s="3">
         <v>300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>500</v>
-      </c>
-      <c r="T58" s="3">
-        <v>600</v>
       </c>
       <c r="U58" s="3">
         <v>600</v>
@@ -5398,17 +5532,17 @@
         <v>600</v>
       </c>
       <c r="W58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="X58" s="3">
         <v>400</v>
       </c>
       <c r="Y58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5418,8 +5552,8 @@
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5439,100 +5573,103 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
-        <v>4000</v>
+        <v>200</v>
       </c>
       <c r="F59" s="3">
-        <v>11400</v>
+        <v>3200</v>
       </c>
       <c r="G59" s="3">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="H59" s="3">
-        <v>2100</v>
+        <v>3200</v>
       </c>
       <c r="I59" s="3">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="J59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K59" s="3">
         <v>8500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>300</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>200</v>
       </c>
       <c r="AF59" s="3">
         <v>200</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
+      <c r="AG59" s="3">
+        <v>200</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>4</v>
@@ -5543,100 +5680,103 @@
       <c r="AJ59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>12500</v>
+      </c>
+      <c r="G60" s="3">
+        <v>18600</v>
+      </c>
+      <c r="H60" s="3">
         <v>11300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K60" s="3">
+        <v>14400</v>
+      </c>
+      <c r="L60" s="3">
+        <v>11400</v>
+      </c>
+      <c r="M60" s="3">
+        <v>12300</v>
+      </c>
+      <c r="N60" s="3">
+        <v>20600</v>
+      </c>
+      <c r="O60" s="3">
+        <v>20300</v>
+      </c>
+      <c r="P60" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Q60" s="3">
+        <v>10700</v>
+      </c>
+      <c r="R60" s="3">
+        <v>8700</v>
+      </c>
+      <c r="S60" s="3">
+        <v>10100</v>
+      </c>
+      <c r="T60" s="3">
+        <v>11900</v>
+      </c>
+      <c r="U60" s="3">
+        <v>13600</v>
+      </c>
+      <c r="V60" s="3">
         <v>12800</v>
       </c>
-      <c r="F60" s="3">
-        <v>18700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>11800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>7500</v>
-      </c>
-      <c r="J60" s="3">
-        <v>14400</v>
-      </c>
-      <c r="K60" s="3">
-        <v>11400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>12300</v>
-      </c>
-      <c r="M60" s="3">
-        <v>20600</v>
-      </c>
-      <c r="N60" s="3">
-        <v>20300</v>
-      </c>
-      <c r="O60" s="3">
-        <v>14000</v>
-      </c>
-      <c r="P60" s="3">
-        <v>10700</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>8700</v>
-      </c>
-      <c r="R60" s="3">
+      <c r="W60" s="3">
+        <v>16400</v>
+      </c>
+      <c r="X60" s="3">
+        <v>21700</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="Z60" s="3">
         <v>10100</v>
       </c>
-      <c r="S60" s="3">
-        <v>11900</v>
-      </c>
-      <c r="T60" s="3">
-        <v>13600</v>
-      </c>
-      <c r="U60" s="3">
-        <v>12800</v>
-      </c>
-      <c r="V60" s="3">
-        <v>16400</v>
-      </c>
-      <c r="W60" s="3">
-        <v>21700</v>
-      </c>
-      <c r="X60" s="3">
-        <v>15700</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>10100</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>6600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>5300</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>3000</v>
       </c>
       <c r="AF60" s="3">
         <v>3000</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>4</v>
+      <c r="AG60" s="3">
+        <v>3000</v>
       </c>
       <c r="AH60" s="3" t="s">
         <v>4</v>
@@ -5647,80 +5787,83 @@
       <c r="AJ60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
+        <v>600</v>
+      </c>
+      <c r="F61" s="3">
         <v>800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>800</v>
+      </c>
+      <c r="H61" s="3">
+        <v>800</v>
+      </c>
+      <c r="I61" s="3">
         <v>900</v>
       </c>
-      <c r="G61" s="3">
-        <v>900</v>
-      </c>
-      <c r="H61" s="3">
-        <v>900</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>200</v>
-      </c>
-      <c r="T61" s="3">
-        <v>300</v>
       </c>
       <c r="U61" s="3">
         <v>300</v>
       </c>
       <c r="V61" s="3">
+        <v>300</v>
+      </c>
+      <c r="W61" s="3">
         <v>400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>600</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5734,14 +5877,14 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>64400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>63500</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5751,43 +5894,46 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
@@ -5795,11 +5941,11 @@
       <c r="P62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -5810,11 +5956,11 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X62" s="3">
         <v>100</v>
@@ -5832,7 +5978,7 @@
         <v>100</v>
       </c>
       <c r="AC62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5843,8 +5989,8 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
+      <c r="AG62" s="3">
+        <v>0</v>
       </c>
       <c r="AH62" s="3" t="s">
         <v>4</v>
@@ -5855,8 +6001,11 @@
       <c r="AJ62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,101 +6322,104 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F66" s="3">
+        <v>13300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>19500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>12200</v>
+      </c>
+      <c r="I66" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="L66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="M66" s="3">
+        <v>13600</v>
+      </c>
+      <c r="N66" s="3">
+        <v>21700</v>
+      </c>
+      <c r="O66" s="3">
+        <v>21500</v>
+      </c>
+      <c r="P66" s="3">
+        <v>15200</v>
+      </c>
+      <c r="Q66" s="3">
         <v>12100</v>
       </c>
-      <c r="E66" s="3">
-        <v>13700</v>
-      </c>
-      <c r="F66" s="3">
-        <v>19500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>12700</v>
-      </c>
-      <c r="H66" s="3">
-        <v>9200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>8600</v>
-      </c>
-      <c r="J66" s="3">
-        <v>15600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>12600</v>
-      </c>
-      <c r="L66" s="3">
-        <v>13600</v>
-      </c>
-      <c r="M66" s="3">
-        <v>21700</v>
-      </c>
-      <c r="N66" s="3">
-        <v>21500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>15200</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
+        <v>8900</v>
+      </c>
+      <c r="S66" s="3">
+        <v>10300</v>
+      </c>
+      <c r="T66" s="3">
         <v>12100</v>
       </c>
-      <c r="Q66" s="3">
-        <v>8900</v>
-      </c>
-      <c r="R66" s="3">
-        <v>10300</v>
-      </c>
-      <c r="S66" s="3">
-        <v>12100</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>67500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>66500</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6271,8 +6429,11 @@
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,101 +6896,104 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-295200</v>
+        <v>-364800</v>
       </c>
       <c r="E72" s="3">
-        <v>-281200</v>
+        <v>-331800</v>
       </c>
       <c r="F72" s="3">
-        <v>-272600</v>
+        <v>-319100</v>
       </c>
       <c r="G72" s="3">
-        <v>-255400</v>
+        <v>-316300</v>
       </c>
       <c r="H72" s="3">
-        <v>-248000</v>
+        <v>-286000</v>
       </c>
       <c r="I72" s="3">
-        <v>-240000</v>
+        <v>-286800</v>
       </c>
       <c r="J72" s="3">
+        <v>-276600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-229100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-215300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-209200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-212000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-198800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-184400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-169600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-155000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-141700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-138500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-137500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-127100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-127500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-118500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-98800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-84400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-74300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>172100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>174200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>119900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>130800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>4</v>
       </c>
@@ -6829,8 +7003,11 @@
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,101 +7324,104 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>91000</v>
+        <v>72800</v>
       </c>
       <c r="E76" s="3">
-        <v>105000</v>
+        <v>88000</v>
       </c>
       <c r="F76" s="3">
-        <v>113600</v>
+        <v>102200</v>
       </c>
       <c r="G76" s="3">
-        <v>130700</v>
+        <v>113400</v>
       </c>
       <c r="H76" s="3">
-        <v>138100</v>
+        <v>124900</v>
       </c>
       <c r="I76" s="3">
-        <v>87000</v>
+        <v>136100</v>
       </c>
       <c r="J76" s="3">
+        <v>85400</v>
+      </c>
+      <c r="K76" s="3">
         <v>97900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>107500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>111100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>103500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>114100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>124100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>130800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>146900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>77700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>93100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>99400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>110800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>125100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>150900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>154000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>174600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>179100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>175600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>177600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>123000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>134000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7245,8 +7431,11 @@
       <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-15300</v>
+        <v>-19500</v>
       </c>
       <c r="E81" s="3">
-        <v>-10700</v>
+        <v>-14800</v>
       </c>
       <c r="F81" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="G81" s="3">
         <v>-17600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H81" s="3">
-        <v>-9100</v>
+        <v>-7900</v>
       </c>
       <c r="I81" s="3">
-        <v>-12300</v>
+        <v>-9000</v>
       </c>
       <c r="J81" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-8900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-15900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-17800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-29500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,25 +7798,26 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
@@ -7663,13 +7862,13 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>500</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -7678,7 +7877,7 @@
         <v>100</v>
       </c>
       <c r="AB83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -7701,11 +7900,14 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
-      <c r="AJ83" s="3" t="s">
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-13400</v>
+        <v>-10800</v>
       </c>
       <c r="E89" s="3">
-        <v>-16500</v>
+        <v>-13000</v>
       </c>
       <c r="F89" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="G89" s="3">
         <v>-12000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="H89" s="3">
-        <v>-12400</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-11600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-11500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ89" s="3" t="s">
+      <c r="AK89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8586,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8390,11 +8611,11 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -8417,11 +8638,11 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -8429,25 +8650,25 @@
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-300</v>
       </c>
       <c r="Z91" s="3">
         <v>-300</v>
       </c>
       <c r="AA91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-100</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
@@ -8456,22 +8677,25 @@
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG91" s="3">
         <v>0</v>
       </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ91" s="3" t="s">
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,88 +8905,91 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>6600</v>
+        <v>19500</v>
       </c>
       <c r="E94" s="3">
-        <v>29800</v>
+        <v>6400</v>
       </c>
       <c r="F94" s="3">
+        <v>29100</v>
+      </c>
+      <c r="G94" s="3">
         <v>3100</v>
       </c>
-      <c r="G94" s="3">
-        <v>8200</v>
-      </c>
       <c r="H94" s="3">
-        <v>-26900</v>
+        <v>7800</v>
       </c>
       <c r="I94" s="3">
-        <v>-4000</v>
+        <v>-26500</v>
       </c>
       <c r="J94" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K94" s="3">
         <v>2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>28800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-36500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>33100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>27100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>19800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>7100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
       </c>
       <c r="AD94" s="3">
         <v>-100</v>
@@ -8768,22 +8998,25 @@
         <v>-100</v>
       </c>
       <c r="AF94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="3" t="s">
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,31 +9053,32 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9479,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9254,16 +9500,16 @@
         <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>58900</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>58000</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2400</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
@@ -9272,163 +9518,166 @@
         <v>-100</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R100" s="3">
         <v>65400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
-      </c>
-      <c r="U100" s="3">
-        <v>-100</v>
       </c>
       <c r="V100" s="3">
         <v>-100</v>
       </c>
       <c r="W100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>54000</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>120400</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>1800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>36200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>36300</v>
       </c>
-      <c r="AJ100" s="3" t="s">
+      <c r="AK100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H101" s="3">
+        <v>800</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
-        <v>400</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="K101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="L101" s="3">
+        <v>900</v>
+      </c>
+      <c r="M101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>300</v>
+      </c>
+      <c r="O101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="R101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="G101" s="3">
-        <v>200</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>900</v>
-      </c>
-      <c r="L101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="O101" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>2600</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="V101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="U101" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
         <v>0</v>
       </c>
@@ -9441,111 +9690,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
-      <c r="AJ101" s="3" t="s">
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6600</v>
+        <v>7900</v>
       </c>
       <c r="E102" s="3">
-        <v>13700</v>
+        <v>-6400</v>
       </c>
       <c r="F102" s="3">
+        <v>13300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-9900</v>
       </c>
-      <c r="G102" s="3">
-        <v>2400</v>
-      </c>
       <c r="H102" s="3">
-        <v>19300</v>
+        <v>2300</v>
       </c>
       <c r="I102" s="3">
-        <v>-15700</v>
+        <v>19000</v>
       </c>
       <c r="J102" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-26900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-47400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>55800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>32600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-8300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-13100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>7100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-23100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-110400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>44800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>113500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>30300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>34700</v>
       </c>
-      <c r="AJ102" s="3" t="s">
+      <c r="AK102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,168 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
@@ -825,11 +828,11 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
@@ -845,8 +848,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -914,28 +917,31 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E9" s="3">
         <v>-100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>300</v>
       </c>
       <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>4</v>
+      <c r="I9" s="3">
+        <v>300</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>4</v>
@@ -1021,29 +1027,32 @@
       <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-200</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1128,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1167,115 +1179,119 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E12" s="3">
         <v>12400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>16000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>12200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5400</v>
-      </c>
-      <c r="U12" s="3">
-        <v>8000</v>
       </c>
       <c r="V12" s="3">
         <v>8000</v>
       </c>
       <c r="W12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="X12" s="3">
         <v>12800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>16400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>23800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>10700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>2900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,13 +1397,16 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>1000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1395,21 +1414,21 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>14800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-8400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1488,8 +1507,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1503,19 +1525,19 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,142 +1656,146 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E17" s="3">
         <v>17300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>-100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>19900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>19300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>14800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-17100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19900</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1776,77 +1805,80 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3">
         <v>-14100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-16200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-31900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-14800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,35 +1916,36 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1922,104 +1955,107 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-500</v>
       </c>
       <c r="U20" s="3">
         <v>-500</v>
       </c>
       <c r="V20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W20" s="3">
         <v>1700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-900</v>
       </c>
       <c r="AG20" s="3">
         <v>-900</v>
       </c>
       <c r="AH20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-15600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-9800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2029,77 +2065,80 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>-13500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-15700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-17700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2148,8 +2187,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>4</v>
@@ -2160,8 +2199,8 @@
       <c r="V22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2205,123 +2244,129 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-13700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-15600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-7100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
@@ -2338,8 +2383,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -2419,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-14800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-15600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-15600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-15900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,35 +3234,38 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3206,184 +3275,190 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
-      </c>
-      <c r="T32" s="3">
-        <v>500</v>
       </c>
       <c r="U32" s="3">
         <v>500</v>
       </c>
       <c r="V32" s="3">
+        <v>500</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2600</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>900</v>
       </c>
       <c r="AG32" s="3">
         <v>900</v>
       </c>
       <c r="AH32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI32" s="3">
         <v>1000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-13700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-15600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-15900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-13700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-15600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-15900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,104 +3871,105 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E41" s="3">
         <v>29200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>21300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>63600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>26600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>62400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>171400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>126500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>138300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>28400</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3893,13 +3979,16 @@
       <c r="AK41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>35700</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3911,71 +4000,71 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>88200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>92600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>63100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>75600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>88500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>123000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>137100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>79400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>52900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>103200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>115900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>32500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>27700</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA42" s="3">
         <v>49300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>38900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>60000</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3988,8 +4077,8 @@
       <c r="AG42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
+      <c r="AH42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
@@ -4000,61 +4089,64 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1700</v>
       </c>
       <c r="M43" s="3">
         <v>1700</v>
       </c>
       <c r="N43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1400</v>
       </c>
       <c r="S43" s="3">
         <v>1400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>4</v>
+      <c r="T43" s="3">
+        <v>1400</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>4</v>
@@ -4071,8 +4163,8 @@
       <c r="Y43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -4107,32 +4199,35 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E44" s="3">
         <v>10800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4148,8 +4243,8 @@
       <c r="O44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4214,104 +4309,107 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E45" s="3">
         <v>38600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>63800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>68200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>89800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>104700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>90500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>74700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>136800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>104100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>126600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>121600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>9800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1200</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4321,104 +4419,107 @@
       <c r="AK45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E46" s="3">
         <v>82100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>97800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>111100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>121000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>135000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>122500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>83000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>107900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>117500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>122000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>112800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>103700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>108000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>139900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>153900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>86100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>103000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>110800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>121200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>138900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>169900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>167700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>183000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>187100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>124200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>181200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>127300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>139100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>26700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>29600</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4428,52 +4529,55 @@
       <c r="AK46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E47" s="3">
         <v>5200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3200</v>
-      </c>
-      <c r="L47" s="3">
-        <v>300</v>
       </c>
       <c r="M47" s="3">
         <v>300</v>
       </c>
       <c r="N47" s="3">
+        <v>300</v>
+      </c>
+      <c r="O47" s="3">
         <v>10100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>28800</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>300</v>
       </c>
       <c r="R47" s="3">
         <v>300</v>
@@ -4503,28 +4607,28 @@
         <v>300</v>
       </c>
       <c r="AA47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB47" s="3">
         <v>200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>57400</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
       <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
         <v>100</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
       <c r="AF47" s="3">
         <v>0</v>
       </c>
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>4</v>
+      <c r="AH47" s="3">
+        <v>0</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>4</v>
@@ -4535,22 +4639,25 @@
       <c r="AK47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1500</v>
       </c>
       <c r="H48" s="3">
         <v>1500</v>
@@ -4559,80 +4666,80 @@
         <v>1500</v>
       </c>
       <c r="J48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K48" s="3">
         <v>1700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1800</v>
       </c>
       <c r="L48" s="3">
         <v>1800</v>
       </c>
       <c r="M48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N48" s="3">
         <v>1900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1600</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1900</v>
       </c>
       <c r="Y48" s="3">
         <v>1900</v>
       </c>
       <c r="Z48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA48" s="3">
         <v>1700</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>700</v>
       </c>
       <c r="AB48" s="3">
         <v>700</v>
       </c>
       <c r="AC48" s="3">
+        <v>700</v>
+      </c>
+      <c r="AD48" s="3">
         <v>500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>300</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>200</v>
       </c>
       <c r="AF48" s="3">
         <v>200</v>
       </c>
       <c r="AG48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH48" s="3">
         <v>100</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4642,25 +4749,28 @@
       <c r="AK48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>100</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
         <v>100</v>
@@ -4669,7 +4779,7 @@
         <v>100</v>
       </c>
       <c r="K49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L49" s="3">
         <v>200</v>
@@ -4681,7 +4791,7 @@
         <v>200</v>
       </c>
       <c r="O49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P49" s="3">
         <v>300</v>
@@ -4696,38 +4806,38 @@
         <v>300</v>
       </c>
       <c r="T49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U49" s="3">
         <v>400</v>
       </c>
       <c r="V49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W49" s="3">
         <v>500</v>
       </c>
       <c r="X49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y49" s="3">
         <v>600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>300</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
       <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
         <v>100</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
       <c r="AE49" s="3">
         <v>0</v>
       </c>
@@ -4737,8 +4847,8 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>4</v>
+      <c r="AH49" s="3">
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>4</v>
@@ -4749,8 +4859,11 @@
       <c r="AK49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4975,7 +5094,7 @@
         <v>200</v>
       </c>
       <c r="F52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -4993,7 +5112,7 @@
         <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
@@ -5020,7 +5139,7 @@
         <v>400</v>
       </c>
       <c r="U52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V52" s="3">
         <v>500</v>
@@ -5029,25 +5148,25 @@
         <v>500</v>
       </c>
       <c r="X52" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
+      <c r="Z52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>4</v>
+      <c r="AC52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD52" s="3">
+        <v>0</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
@@ -5058,8 +5177,8 @@
       <c r="AG52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH52" s="3">
-        <v>0</v>
+      <c r="AH52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI52" s="3">
         <v>0</v>
@@ -5070,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,104 +5299,107 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E54" s="3">
         <v>88900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>99700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>115500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>132900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>137100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>145200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>93800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>113400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>124700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>125200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>135700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>139300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>142900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>155800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>88000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>105200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>113300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>123800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>141900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>173400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>170500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>185400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>188300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>182300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>181800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>127600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>139400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>26900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29800</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5284,8 +5409,11 @@
       <c r="AK54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,103 +5491,104 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E57" s="3">
         <v>13100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>14500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5000</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>2800</v>
       </c>
       <c r="AG57" s="3">
         <v>2800</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>4</v>
+      <c r="AH57" s="3">
+        <v>2800</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>4</v>
@@ -5469,8 +5599,11 @@
       <c r="AK57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5520,13 +5653,13 @@
         <v>400</v>
       </c>
       <c r="S58" s="3">
+        <v>400</v>
+      </c>
+      <c r="T58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>500</v>
-      </c>
-      <c r="U58" s="3">
-        <v>600</v>
       </c>
       <c r="V58" s="3">
         <v>600</v>
@@ -5535,17 +5668,17 @@
         <v>600</v>
       </c>
       <c r="X58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Y58" s="3">
         <v>400</v>
       </c>
       <c r="Z58" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA58" s="3">
         <v>300</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5555,8 +5688,8 @@
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5576,8 +5709,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5585,10 +5721,10 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3200</v>
       </c>
       <c r="G59" s="3">
         <v>3200</v>
@@ -5597,82 +5733,82 @@
         <v>3200</v>
       </c>
       <c r="I59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>300</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>200</v>
       </c>
       <c r="AG59" s="3">
         <v>200</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>4</v>
+      <c r="AH59" s="3">
+        <v>200</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>4</v>
@@ -5683,103 +5819,106 @@
       <c r="AK59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E60" s="3">
         <v>15500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>16400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>21700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>15700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>6600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5300</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>3000</v>
       </c>
       <c r="AG60" s="3">
         <v>3000</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>4</v>
+      <c r="AH60" s="3">
+        <v>3000</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>4</v>
@@ -5790,19 +5929,22 @@
       <c r="AK60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E61" s="3">
         <v>600</v>
       </c>
       <c r="F61" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G61" s="3">
         <v>800</v>
@@ -5811,62 +5953,62 @@
         <v>800</v>
       </c>
       <c r="I61" s="3">
+        <v>800</v>
+      </c>
+      <c r="J61" s="3">
         <v>900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>200</v>
-      </c>
-      <c r="U61" s="3">
-        <v>300</v>
       </c>
       <c r="V61" s="3">
         <v>300</v>
       </c>
       <c r="W61" s="3">
+        <v>300</v>
+      </c>
+      <c r="X61" s="3">
         <v>400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>600</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5880,14 +6022,14 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>64400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>63500</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
       <c r="AI61" s="3">
         <v>0</v>
       </c>
@@ -5897,8 +6039,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5923,20 +6068,20 @@
       <c r="J62" s="3">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
@@ -5944,11 +6089,11 @@
       <c r="Q62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
@@ -5959,11 +6104,11 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="3">
         <v>100</v>
@@ -5981,7 +6126,7 @@
         <v>100</v>
       </c>
       <c r="AD62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5992,8 +6137,8 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
+      <c r="AH62" s="3">
+        <v>0</v>
       </c>
       <c r="AI62" s="3" t="s">
         <v>4</v>
@@ -6004,8 +6149,11 @@
       <c r="AK62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,104 +6479,107 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E66" s="3">
         <v>16100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>67500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>66500</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6432,8 +6589,11 @@
       <c r="AK66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,104 +7069,107 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-343900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-364800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-331800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-319100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-316300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-286000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-286800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-276600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-229100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-215300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-209200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-212000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-198800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-184400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-169600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-155000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-141700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-138500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-137500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-127100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-127500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-118500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-98800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-84400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-74300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>172100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>174200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>119900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>130800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7006,8 +7179,11 @@
       <c r="AK72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,104 +7509,107 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E76" s="3">
         <v>72800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>88000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>102200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>113400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>124900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>136100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>85400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>97900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>107500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>111100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>103500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>114100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>124100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>130800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>146900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>77700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>93100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>99400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>110800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>125100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>150900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>154000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>174600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>179100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>175600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>177600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>123000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>134000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7434,8 +7619,11 @@
       <c r="AK76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-13700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-15600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-15900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-29500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,28 +7996,29 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -7865,13 +8063,13 @@
         <v>200</v>
       </c>
       <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>100</v>
       </c>
       <c r="AA83" s="3">
         <v>100</v>
@@ -7880,7 +8078,7 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -7903,11 +8101,14 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
-      <c r="AK83" s="3" t="s">
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-13000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-12000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-11400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-11000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-11500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-18900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-32000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK89" s="3" t="s">
+      <c r="AL89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8614,11 +8834,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -8641,11 +8861,11 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -8653,25 +8873,25 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-900</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-300</v>
       </c>
       <c r="AA91" s="3">
         <v>-300</v>
       </c>
       <c r="AB91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-100</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
@@ -8680,22 +8900,25 @@
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK91" s="3" t="s">
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,91 +9134,94 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>19500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>6400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>29100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>3100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>28800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-36500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>6200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>3200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>33100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>27100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>19800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>7100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-100</v>
       </c>
       <c r="AE94" s="3">
         <v>-100</v>
@@ -9001,22 +9230,25 @@
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK94" s="3" t="s">
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9080,8 +9313,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,13 +9724,16 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>700</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
@@ -9503,16 +9748,16 @@
         <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>58000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>2400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
@@ -9521,166 +9766,169 @@
         <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
         <v>-100</v>
       </c>
       <c r="R100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S100" s="3">
         <v>65400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
-      </c>
-      <c r="V100" s="3">
-        <v>-100</v>
       </c>
       <c r="W100" s="3">
         <v>-100</v>
       </c>
       <c r="X100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>54000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>120400</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
         <v>0</v>
       </c>
       <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>1800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>36300</v>
       </c>
-      <c r="AK100" s="3" t="s">
+      <c r="AL100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
         <v>0</v>
       </c>
@@ -9693,114 +9941,120 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
-      <c r="AK101" s="3" t="s">
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E102" s="3">
         <v>7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-47400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>55800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-23100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-110400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>44800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>113500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>34700</v>
       </c>
-      <c r="AK102" s="3" t="s">
+      <c r="AL102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,174 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
       <c r="G8" s="3">
         <v>0</v>
       </c>
@@ -831,11 +835,11 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
@@ -851,8 +855,8 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -920,31 +924,34 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
         <v>2900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>-100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>300</v>
       </c>
       <c r="I9" s="3">
         <v>300</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>4</v>
+      <c r="J9" s="3">
+        <v>300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -1030,32 +1037,35 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-200</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,118 +1193,122 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="3">
         <v>7100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>12400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>16000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>10100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5400</v>
-      </c>
-      <c r="V12" s="3">
-        <v>8000</v>
       </c>
       <c r="W12" s="3">
         <v>8000</v>
       </c>
       <c r="X12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Y12" s="3">
         <v>12800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>16400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>23800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>10700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>5500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>6000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>2900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>3500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,13 +1417,16 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>1000</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>4</v>
@@ -1417,21 +1437,21 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>14800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1510,8 +1530,11 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1519,7 +1542,7 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1528,19 +1551,19 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,148 +1683,152 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9100</v>
+        <v>14100</v>
       </c>
       <c r="E17" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F17" s="3">
         <v>17300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>-100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>14800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>9200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>8100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-9100</v>
+        <v>-14100</v>
       </c>
       <c r="E18" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-17100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-19900</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1808,77 +1838,80 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-31900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-14800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,38 +1950,39 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1958,107 +1992,110 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-500</v>
       </c>
       <c r="V20" s="3">
         <v>-500</v>
       </c>
       <c r="W20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X20" s="3">
         <v>1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-900</v>
       </c>
       <c r="AH20" s="3">
         <v>-900</v>
       </c>
       <c r="AI20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4800</v>
+        <v>-9400</v>
       </c>
       <c r="E21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-20200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-15600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2068,77 +2105,80 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-12800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-17700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL21" s="3" t="s">
+      <c r="AM21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2190,8 +2230,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>4</v>
@@ -2202,8 +2242,8 @@
       <c r="W22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2247,129 +2287,135 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-9000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-15600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-7100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
+      <c r="F24" s="3">
+        <v>0</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>4</v>
@@ -2386,8 +2432,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-15600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,38 +3304,41 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3278,187 +3348,193 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>500</v>
       </c>
       <c r="V32" s="3">
         <v>500</v>
       </c>
       <c r="W32" s="3">
+        <v>500</v>
+      </c>
+      <c r="X32" s="3">
         <v>-1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2600</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>900</v>
       </c>
       <c r="AH32" s="3">
         <v>900</v>
       </c>
       <c r="AI32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>2400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-15600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-15600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,107 +3958,108 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E41" s="3">
         <v>19000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>29200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>46100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>63600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>26600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>62400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>171400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>126500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>138300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>28400</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3982,13 +4069,16 @@
       <c r="AL41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>35700</v>
+        <v>20100</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4003,71 +4093,71 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>72600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>88200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>92600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>63100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>75600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>88500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>123000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>137100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>79400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>52900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>103200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>115900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>32500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>27700</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB42" s="3">
         <v>49300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>38900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>60000</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4080,8 +4170,8 @@
       <c r="AH42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI42" s="3">
-        <v>0</v>
+      <c r="AI42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ42" s="3">
         <v>0</v>
@@ -4092,8 +4182,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4101,55 +4194,55 @@
         <v>1800</v>
       </c>
       <c r="E43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1600</v>
-      </c>
-      <c r="M43" s="3">
-        <v>1700</v>
       </c>
       <c r="N43" s="3">
         <v>1700</v>
       </c>
       <c r="O43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
-      </c>
-      <c r="S43" s="3">
-        <v>1400</v>
       </c>
       <c r="T43" s="3">
         <v>1400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>4</v>
+      <c r="U43" s="3">
+        <v>1400</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>4</v>
@@ -4166,8 +4259,8 @@
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -4202,35 +4295,38 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E44" s="3">
         <v>7100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>12600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4246,8 +4342,8 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4312,107 +4408,110 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10500</v>
+        <v>6200</v>
       </c>
       <c r="E45" s="3">
+        <v>45900</v>
+      </c>
+      <c r="F45" s="3">
         <v>38600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>63800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>68200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>89800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>104700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>90500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>74700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>11000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>136800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>104100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>126600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>121600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1200</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4422,107 +4521,110 @@
       <c r="AL45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E46" s="3">
         <v>74200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>82100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>97800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>111100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>121000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>135000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>122500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>83000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>107900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>117500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>122000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>112800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>103700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>108000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>139900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>153900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>86100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>103000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>110800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>121200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>138900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>169900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>167700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>183000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>187100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>124200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>181200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>127300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>139100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>26700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>29600</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4532,55 +4634,58 @@
       <c r="AL46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3">
         <v>3200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>5200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3200</v>
-      </c>
-      <c r="M47" s="3">
-        <v>300</v>
       </c>
       <c r="N47" s="3">
         <v>300</v>
       </c>
       <c r="O47" s="3">
+        <v>300</v>
+      </c>
+      <c r="P47" s="3">
         <v>10100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>29500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>28800</v>
-      </c>
-      <c r="R47" s="3">
-        <v>300</v>
       </c>
       <c r="S47" s="3">
         <v>300</v>
@@ -4610,28 +4715,28 @@
         <v>300</v>
       </c>
       <c r="AB47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC47" s="3">
         <v>200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>57400</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
-      </c>
       <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
         <v>100</v>
       </c>
-      <c r="AF47" s="3">
-        <v>0</v>
-      </c>
       <c r="AG47" s="3">
         <v>0</v>
       </c>
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>4</v>
+      <c r="AI47" s="3">
+        <v>0</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>4</v>
@@ -4642,25 +4747,28 @@
       <c r="AL47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1500</v>
       </c>
       <c r="I48" s="3">
         <v>1500</v>
@@ -4669,80 +4777,80 @@
         <v>1500</v>
       </c>
       <c r="K48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L48" s="3">
         <v>1700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1800</v>
       </c>
       <c r="M48" s="3">
         <v>1800</v>
       </c>
       <c r="N48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O48" s="3">
         <v>1900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1600</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1900</v>
       </c>
       <c r="Z48" s="3">
         <v>1900</v>
       </c>
       <c r="AA48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1700</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>700</v>
       </c>
       <c r="AC48" s="3">
         <v>700</v>
       </c>
       <c r="AD48" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE48" s="3">
         <v>500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>300</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>200</v>
       </c>
       <c r="AG48" s="3">
         <v>200</v>
       </c>
       <c r="AH48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI48" s="3">
         <v>100</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4752,8 +4860,11 @@
       <c r="AL48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4767,13 +4878,13 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>100</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>100</v>
@@ -4782,7 +4893,7 @@
         <v>100</v>
       </c>
       <c r="L49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M49" s="3">
         <v>200</v>
@@ -4794,7 +4905,7 @@
         <v>200</v>
       </c>
       <c r="P49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q49" s="3">
         <v>300</v>
@@ -4809,38 +4920,38 @@
         <v>300</v>
       </c>
       <c r="U49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="V49" s="3">
         <v>400</v>
       </c>
       <c r="W49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X49" s="3">
         <v>500</v>
       </c>
       <c r="Y49" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z49" s="3">
         <v>600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>300</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
       <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
         <v>100</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
-      </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
@@ -4850,8 +4961,8 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>4</v>
+      <c r="AI49" s="3">
+        <v>0</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>4</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5091,13 +5211,13 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
@@ -5115,7 +5235,7 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
@@ -5142,7 +5262,7 @@
         <v>400</v>
       </c>
       <c r="V52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="W52" s="3">
         <v>500</v>
@@ -5151,25 +5271,25 @@
         <v>500</v>
       </c>
       <c r="Y52" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z52" s="3">
         <v>600</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>4</v>
+      <c r="AA52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>4</v>
+      <c r="AD52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>4</v>
@@ -5180,8 +5300,8 @@
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
+      <c r="AI52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ52" s="3">
         <v>0</v>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,107 +5425,110 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E54" s="3">
         <v>78700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>88900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>99700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>115500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>132900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>145200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>93800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>113400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>124700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>125200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>135700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>139300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>142900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>155800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>88000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>105200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>113300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>123800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>141900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>173400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>170500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>185400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>188300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>182300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>181800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>127600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>139400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>26900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>29800</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5412,8 +5538,11 @@
       <c r="AL54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,106 +5622,107 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11800</v>
+        <v>1500</v>
       </c>
       <c r="E57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F57" s="3">
         <v>13100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>9400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>14500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>20300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>14300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>8400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5000</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>2800</v>
       </c>
       <c r="AH57" s="3">
         <v>2800</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>4</v>
+      <c r="AI57" s="3">
+        <v>2800</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>4</v>
@@ -5602,8 +5733,11 @@
       <c r="AL57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5656,13 +5790,13 @@
         <v>400</v>
       </c>
       <c r="T58" s="3">
+        <v>400</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>500</v>
-      </c>
-      <c r="V58" s="3">
-        <v>600</v>
       </c>
       <c r="W58" s="3">
         <v>600</v>
@@ -5671,17 +5805,17 @@
         <v>600</v>
       </c>
       <c r="Y58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="Z58" s="3">
         <v>400</v>
       </c>
       <c r="AA58" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB58" s="3">
         <v>300</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5691,8 +5825,8 @@
       <c r="AE58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5712,22 +5846,25 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>300</v>
+        <v>7300</v>
       </c>
       <c r="E59" s="3">
         <v>300</v>
       </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
         <v>200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3200</v>
       </c>
       <c r="H59" s="3">
         <v>3200</v>
@@ -5736,82 +5873,82 @@
         <v>3200</v>
       </c>
       <c r="J59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>300</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>200</v>
       </c>
       <c r="AH59" s="3">
         <v>200</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>4</v>
+      <c r="AI59" s="3">
+        <v>200</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>4</v>
@@ -5822,106 +5959,109 @@
       <c r="AL59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E60" s="3">
         <v>14700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>21700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>6600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5300</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>3000</v>
       </c>
       <c r="AH60" s="3">
         <v>3000</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>4</v>
+      <c r="AI60" s="3">
+        <v>3000</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>4</v>
@@ -5932,22 +6072,25 @@
       <c r="AL60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
-      </c>
-      <c r="E61" s="3">
-        <v>600</v>
       </c>
       <c r="F61" s="3">
         <v>600</v>
       </c>
       <c r="G61" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="H61" s="3">
         <v>800</v>
@@ -5956,62 +6099,62 @@
         <v>800</v>
       </c>
       <c r="J61" s="3">
+        <v>800</v>
+      </c>
+      <c r="K61" s="3">
         <v>900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>200</v>
-      </c>
-      <c r="V61" s="3">
-        <v>300</v>
       </c>
       <c r="W61" s="3">
         <v>300</v>
       </c>
       <c r="X61" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y61" s="3">
         <v>400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>600</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -6025,14 +6168,14 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>64400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>63500</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6071,20 +6217,20 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
@@ -6092,11 +6238,11 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
@@ -6107,11 +6253,11 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3">
         <v>100</v>
@@ -6129,7 +6275,7 @@
         <v>100</v>
       </c>
       <c r="AE62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6140,8 +6286,8 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
+      <c r="AI62" s="3">
+        <v>0</v>
       </c>
       <c r="AJ62" s="3" t="s">
         <v>4</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,107 +6637,110 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E66" s="3">
         <v>15100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>67500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>66500</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6592,8 +6750,11 @@
       <c r="AL66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,107 +7243,110 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-368000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-343900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-364800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-331800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-319100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-316300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-286000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-286800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-276600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-229100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-215300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-209200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-212000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-198800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-184400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-169600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-155000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-141700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-138500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-137500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-127100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-127500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-118500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-98800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-84400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-74300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>172100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>174200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>119900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>130800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7182,8 +7356,11 @@
       <c r="AL72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,107 +7695,110 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E76" s="3">
         <v>63600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>88000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>102200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>113400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>124900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>136100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>85400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>97900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>107500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>111100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>103500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>114100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>124100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>130800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>146900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>77700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>93100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>99400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>110800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>125100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>150900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>154000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>174600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>179100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>175600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>177600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>123000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>134000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7622,8 +7808,11 @@
       <c r="AL76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-15600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,31 +8195,32 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -8066,13 +8265,13 @@
         <v>200</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>500</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
@@ -8081,7 +8280,7 @@
         <v>100</v>
       </c>
       <c r="AD83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -8104,11 +8303,14 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
-      <c r="AL83" s="3" t="s">
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-14000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-11000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AL89" s="3" t="s">
+      <c r="AM89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8837,11 +9058,11 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -8864,11 +9085,11 @@
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -8876,25 +9097,25 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-300</v>
       </c>
       <c r="AB91" s="3">
         <v>-300</v>
       </c>
       <c r="AC91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-100</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
@@ -8903,22 +9124,25 @@
         <v>-100</v>
       </c>
       <c r="AH91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
       </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
-      <c r="AK91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL91" s="3" t="s">
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,94 +9364,97 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E94" s="3">
         <v>2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>19500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>29100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>5400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>28800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>6200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>3200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>33100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>27100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-24200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>19800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>7100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
@@ -9233,22 +9463,25 @@
         <v>-100</v>
       </c>
       <c r="AH94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AI94" s="3">
         <v>0</v>
       </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-100</v>
       </c>
-      <c r="AK94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL94" s="3" t="s">
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9316,8 +9550,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,16 +9970,19 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
@@ -9751,16 +9997,16 @@
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
         <v>58000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>2400</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-100</v>
       </c>
       <c r="N100" s="3">
         <v>-100</v>
@@ -9769,169 +10015,172 @@
         <v>-100</v>
       </c>
       <c r="P100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R100" s="3">
         <v>-100</v>
       </c>
       <c r="S100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T100" s="3">
         <v>65400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>400</v>
-      </c>
-      <c r="W100" s="3">
-        <v>-100</v>
       </c>
       <c r="X100" s="3">
         <v>-100</v>
       </c>
       <c r="Y100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>54000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>120400</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>36200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>36300</v>
       </c>
-      <c r="AL100" s="3" t="s">
+      <c r="AM100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
         <v>0</v>
       </c>
@@ -9944,117 +10193,123 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
-      <c r="AL101" s="3" t="s">
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-47400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>55800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-18800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-23100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-110400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>44800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>113500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>30300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>34700</v>
       </c>
-      <c r="AL102" s="3" t="s">
+      <c r="AM102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,166 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -825,12 +829,12 @@
       <c r="E8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -838,11 +842,11 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
@@ -858,8 +862,8 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
@@ -927,34 +931,37 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>2900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>-100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>300</v>
       </c>
       <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>4</v>
+      <c r="K9" s="3">
+        <v>300</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>4</v>
@@ -1040,35 +1047,38 @@
       <c r="AM9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>-2900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
@@ -1153,8 +1163,11 @@
       <c r="AM10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1194,121 +1207,125 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>12400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>16000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>8100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>10100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5400</v>
-      </c>
-      <c r="W12" s="3">
-        <v>8000</v>
       </c>
       <c r="X12" s="3">
         <v>8000</v>
       </c>
       <c r="Y12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="Z12" s="3">
         <v>12800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>16400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>23800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>9200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>10700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>6000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>6000</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>2900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>2800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>6200</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1437,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1440,21 +1460,21 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>14800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1533,19 +1553,22 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1554,19 +1577,19 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1646,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,154 +1710,158 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3">
         <v>14100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>19900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>16200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>19300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>9300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>10600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-17100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
@@ -1841,77 +1871,80 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3">
         <v>-14100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-14800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-16200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-31900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-14800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,41 +1984,42 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
@@ -1995,110 +2029,113 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-700</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-500</v>
       </c>
       <c r="W20" s="3">
         <v>-500</v>
       </c>
       <c r="X20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-900</v>
       </c>
       <c r="AI20" s="3">
         <v>-900</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-6000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-15600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-11300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-20800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2108,82 +2145,85 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-13500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-12800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-10800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-17700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-12100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM21" s="3" t="s">
+      <c r="AN21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -2233,8 +2273,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
@@ -2245,8 +2285,8 @@
       <c r="X22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2290,135 +2330,141 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-15600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-7100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>4</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>4</v>
@@ -2435,8 +2481,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2516,8 +2562,11 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-15600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3081,8 +3142,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,41 +3374,44 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
         <v>4500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3351,190 +3421,196 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>700</v>
-      </c>
-      <c r="V32" s="3">
-        <v>500</v>
       </c>
       <c r="W32" s="3">
         <v>500</v>
       </c>
       <c r="X32" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2600</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>900</v>
       </c>
       <c r="AI32" s="3">
         <v>900</v>
       </c>
       <c r="AJ32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK32" s="3">
         <v>1000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-15600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-15600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,110 +4045,111 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3">
         <v>51100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>46100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>63600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>26600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>62400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>171400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>126500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>138300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>24800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>28400</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>4</v>
       </c>
@@ -4072,17 +4159,20 @@
       <c r="AM41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>20100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -4096,71 +4186,71 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>88200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>92600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>63100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>75600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>88500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>123000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>137100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>79400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>52900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>103200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>115900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>32500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>27700</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC42" s="3">
         <v>49300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>38900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>60000</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4173,8 +4263,8 @@
       <c r="AI42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
+      <c r="AJ42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK42" s="3">
         <v>0</v>
@@ -4185,67 +4275,70 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>1800</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E43" s="3">
         <v>1800</v>
       </c>
       <c r="F43" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1600</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1700</v>
       </c>
       <c r="O43" s="3">
         <v>1700</v>
       </c>
       <c r="P43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1400</v>
       </c>
       <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>4</v>
+      <c r="V43" s="3">
+        <v>1400</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>4</v>
@@ -4262,8 +4355,8 @@
       <c r="AA43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
@@ -4298,38 +4391,41 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3">
         <v>7500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4345,8 +4441,8 @@
       <c r="Q44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -4411,110 +4507,113 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3">
         <v>6200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>45900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>63800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>68200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>89800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>104700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>90500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>74700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>136800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>104100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>126600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>121600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>4</v>
       </c>
@@ -4524,110 +4623,113 @@
       <c r="AM45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3">
         <v>92500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>82100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>111100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>121000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>135000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>83000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>107900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>117500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>122000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>112800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>103700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>108000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>139900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>153900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>86100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>103000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>110800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>121200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>138900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>169900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>167700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>183000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>187100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>124200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>181200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>127300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>139100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>4</v>
       </c>
@@ -4637,58 +4739,61 @@
       <c r="AM46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
       </c>
       <c r="P47" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q47" s="3">
         <v>10100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>29500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>28800</v>
-      </c>
-      <c r="S47" s="3">
-        <v>300</v>
       </c>
       <c r="T47" s="3">
         <v>300</v>
@@ -4718,28 +4823,28 @@
         <v>300</v>
       </c>
       <c r="AC47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD47" s="3">
         <v>200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>57400</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
         <v>100</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
       <c r="AH47" s="3">
         <v>0</v>
       </c>
       <c r="AI47" s="3">
         <v>0</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>4</v>
+      <c r="AJ47" s="3">
+        <v>0</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>4</v>
@@ -4750,28 +4855,31 @@
       <c r="AM47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3">
         <v>1000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1500</v>
       </c>
       <c r="J48" s="3">
         <v>1500</v>
@@ -4780,80 +4888,80 @@
         <v>1500</v>
       </c>
       <c r="L48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M48" s="3">
         <v>1700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1800</v>
       </c>
       <c r="N48" s="3">
         <v>1800</v>
       </c>
       <c r="O48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P48" s="3">
         <v>1900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1600</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>1900</v>
       </c>
       <c r="AA48" s="3">
         <v>1900</v>
       </c>
       <c r="AB48" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AC48" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>700</v>
       </c>
       <c r="AD48" s="3">
         <v>700</v>
       </c>
       <c r="AE48" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF48" s="3">
         <v>500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>300</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>200</v>
       </c>
       <c r="AH48" s="3">
         <v>200</v>
       </c>
       <c r="AI48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>100</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>4</v>
       </c>
@@ -4863,17 +4971,20 @@
       <c r="AM48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3">
         <v>100</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -4881,13 +4992,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>100</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -4896,7 +5007,7 @@
         <v>100</v>
       </c>
       <c r="M49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N49" s="3">
         <v>200</v>
@@ -4908,7 +5019,7 @@
         <v>200</v>
       </c>
       <c r="Q49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R49" s="3">
         <v>300</v>
@@ -4923,38 +5034,38 @@
         <v>300</v>
       </c>
       <c r="V49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W49" s="3">
         <v>400</v>
       </c>
       <c r="X49" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y49" s="3">
         <v>500</v>
       </c>
       <c r="Z49" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA49" s="3">
         <v>600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>300</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
       <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
         <v>100</v>
       </c>
-      <c r="AF49" s="3">
-        <v>0</v>
-      </c>
       <c r="AG49" s="3">
         <v>0</v>
       </c>
@@ -4964,8 +5075,8 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>4</v>
+      <c r="AJ49" s="3">
+        <v>0</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>4</v>
@@ -4976,8 +5087,11 @@
       <c r="AM49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,25 +5319,28 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="3">
         <v>200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>300</v>
-      </c>
-      <c r="F52" s="3">
-        <v>200</v>
       </c>
       <c r="G52" s="3">
         <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
@@ -5238,7 +5358,7 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
@@ -5265,7 +5385,7 @@
         <v>400</v>
       </c>
       <c r="W52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X52" s="3">
         <v>500</v>
@@ -5274,25 +5394,25 @@
         <v>500</v>
       </c>
       <c r="Z52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA52" s="3">
         <v>600</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
+      <c r="AB52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
+      <c r="AE52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="3">
+        <v>0</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>4</v>
@@ -5303,8 +5423,8 @@
       <c r="AI52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ52" s="3">
-        <v>0</v>
+      <c r="AJ52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK52" s="3">
         <v>0</v>
@@ -5315,8 +5435,11 @@
       <c r="AM52" s="3">
         <v>0</v>
       </c>
+      <c r="AN52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,110 +5551,113 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3">
         <v>94000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>78700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>88900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>99700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>115500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>132900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>137100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>145200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>93800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>113400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>124700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>125200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>135700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>139300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>142900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>155800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>88000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>105200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>113300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>123800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>141900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>173400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>170500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>185400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>188300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>182300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>181800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>127600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>139400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>26900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29800</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>4</v>
       </c>
@@ -5541,8 +5667,11 @@
       <c r="AM54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,109 +5753,110 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>10300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>9300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>14500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>20300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>14300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>5000</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>2800</v>
       </c>
       <c r="AI57" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>4</v>
+      <c r="AJ57" s="3">
+        <v>2800</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>4</v>
@@ -5736,13 +5867,16 @@
       <c r="AM57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>400</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
@@ -5793,13 +5927,13 @@
         <v>400</v>
       </c>
       <c r="U58" s="3">
+        <v>400</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>600</v>
       </c>
       <c r="X58" s="3">
         <v>600</v>
@@ -5808,17 +5942,17 @@
         <v>600</v>
       </c>
       <c r="Z58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA58" s="3">
         <v>400</v>
       </c>
       <c r="AB58" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC58" s="3">
         <v>300</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>4</v>
       </c>
@@ -5828,8 +5962,8 @@
       <c r="AF58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5849,25 +5983,28 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3">
         <v>7300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
       </c>
       <c r="F59" s="3">
         <v>300</v>
       </c>
       <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
         <v>200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3200</v>
       </c>
       <c r="I59" s="3">
         <v>3200</v>
@@ -5876,82 +6013,82 @@
         <v>3200</v>
       </c>
       <c r="K59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>300</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>200</v>
       </c>
       <c r="AI59" s="3">
         <v>200</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>4</v>
+      <c r="AJ59" s="3">
+        <v>200</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>4</v>
@@ -5962,109 +6099,112 @@
       <c r="AM59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
         <v>17500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>14700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>8700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>21700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5300</v>
-      </c>
-      <c r="AH60" s="3">
-        <v>3000</v>
       </c>
       <c r="AI60" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>4</v>
+      <c r="AJ60" s="3">
+        <v>3000</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>4</v>
@@ -6075,25 +6215,28 @@
       <c r="AM60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>400</v>
-      </c>
-      <c r="F61" s="3">
-        <v>600</v>
       </c>
       <c r="G61" s="3">
         <v>600</v>
       </c>
       <c r="H61" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I61" s="3">
         <v>800</v>
@@ -6102,62 +6245,62 @@
         <v>800</v>
       </c>
       <c r="K61" s="3">
+        <v>800</v>
+      </c>
+      <c r="L61" s="3">
         <v>900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>200</v>
-      </c>
-      <c r="W61" s="3">
-        <v>300</v>
       </c>
       <c r="X61" s="3">
         <v>300</v>
       </c>
       <c r="Y61" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z61" s="3">
         <v>400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>600</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6171,14 +6314,14 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>64400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>63500</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
@@ -6188,13 +6331,16 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -6220,20 +6366,20 @@
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
@@ -6241,11 +6387,11 @@
       <c r="S62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>4</v>
@@ -6256,11 +6402,11 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3">
         <v>100</v>
@@ -6278,7 +6424,7 @@
         <v>100</v>
       </c>
       <c r="AF62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -6289,8 +6435,8 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>4</v>
+      <c r="AJ62" s="3">
+        <v>0</v>
       </c>
       <c r="AK62" s="3" t="s">
         <v>4</v>
@@ -6301,8 +6447,11 @@
       <c r="AM62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,110 +6795,113 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3">
         <v>17900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>21700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>22500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>67500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>66500</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>4</v>
       </c>
@@ -6753,8 +6911,11 @@
       <c r="AM66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7301,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,110 +7417,113 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>-368000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-343900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-364800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-331800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-319100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-316300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-286000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-286800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-276600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-229100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-215300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-209200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-212000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-198800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-184400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-169600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-155000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-141700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-138500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-137500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-127100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-127500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-118500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-98800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-84400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-74300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>172100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>174200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>119900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>130800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>4</v>
       </c>
@@ -7359,8 +7533,11 @@
       <c r="AM72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,110 +7881,113 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3">
         <v>76200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>63600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>88000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>102200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>113400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>124900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>136100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>85400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>97900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>107500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>111100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>103500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>114100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>124100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>130800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>146900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>77700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>93100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>99400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>110800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>125100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>150900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>154000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>174600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>179100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>175600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>177600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>123000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>134000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>4</v>
       </c>
@@ -7811,8 +7997,11 @@
       <c r="AM76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-15600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-15900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-29500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,8 +8394,9 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8205,25 +8404,25 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>100</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -8268,13 +8467,13 @@
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>500</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
@@ -8283,7 +8482,7 @@
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
@@ -8306,11 +8505,14 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
-      <c r="AM83" s="3" t="s">
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9088,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-13600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-11000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-9700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-32000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM89" s="3" t="s">
+      <c r="AN89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,13 +9248,14 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -9061,11 +9282,11 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -9088,11 +9309,11 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -9100,25 +9321,25 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-900</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-300</v>
       </c>
       <c r="AC91" s="3">
         <v>-300</v>
       </c>
       <c r="AD91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-100</v>
       </c>
       <c r="AG91" s="3">
         <v>-100</v>
@@ -9127,22 +9348,25 @@
         <v>-100</v>
       </c>
       <c r="AI91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-100</v>
       </c>
-      <c r="AL91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM91" s="3" t="s">
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,97 +9594,100 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E94" s="3">
         <v>19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>19500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>6400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>29100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>28800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-36500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>6200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>3200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>33100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>27100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>19800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>7100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-100</v>
       </c>
       <c r="AG94" s="3">
         <v>-100</v>
@@ -9466,22 +9696,25 @@
         <v>-100</v>
       </c>
       <c r="AI94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-100</v>
       </c>
-      <c r="AL94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM94" s="3" t="s">
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9553,8 +9787,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9634,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,19 +10216,22 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>29200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
@@ -10000,16 +10246,16 @@
         <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>58000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2400</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
@@ -10018,172 +10264,175 @@
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>-100</v>
       </c>
       <c r="T100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U100" s="3">
         <v>65400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
-      </c>
-      <c r="X100" s="3">
-        <v>-100</v>
       </c>
       <c r="Y100" s="3">
         <v>-100</v>
       </c>
       <c r="Z100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>54000</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>120400</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
         <v>0</v>
       </c>
       <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>1800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>36200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>36300</v>
       </c>
-      <c r="AM100" s="3" t="s">
+      <c r="AN100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
         <v>0</v>
       </c>
@@ -10196,120 +10445,126 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
-      <c r="AM101" s="3" t="s">
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>31200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-47400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>55800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-110400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>44800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>113500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>30300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>34700</v>
       </c>
-      <c r="AM102" s="3" t="s">
+      <c r="AN102" s="3" t="s">
         <v>4</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>IFRX</t>
   </si>
@@ -656,210 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
         <v>100</v>
       </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
@@ -872,11 +879,11 @@
       <c r="R8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
@@ -941,44 +948,50 @@
       <c r="AO8" s="3">
         <v>0</v>
       </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>0</v>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>2800</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
         <v>2900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>-100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1060,43 +1073,49 @@
       <c r="AO9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>0</v>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E10" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>-2800</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>-2900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>-300</v>
       </c>
       <c r="L10" s="3">
         <v>-200</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>4</v>
+      <c r="M10" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N10" s="3">
+        <v>-200</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>4</v>
@@ -1179,8 +1198,14 @@
       <c r="AO10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,127 +1247,135 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F12" s="3">
         <v>7300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>8500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>7100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>12400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>10700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>7900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>8900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>7700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>11900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>16000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>9200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>8100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>12200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>11400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>11000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>10100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>12000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>5200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>5800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>5400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>8000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>8000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>12800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>16400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>23800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>9200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>10700</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>6000</v>
-      </c>
-      <c r="AG12" s="3">
-        <v>5500</v>
       </c>
       <c r="AH12" s="3">
         <v>6000</v>
       </c>
       <c r="AI12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>6000</v>
+      </c>
+      <c r="AK12" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>2900</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AM12" s="3">
         <v>3500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AN12" s="3">
         <v>2800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AO12" s="3">
         <v>6200</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AP12" s="3">
         <v>1200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AQ12" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,23 +1493,29 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-600</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="3">
         <v>-1100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1486,24 +1525,24 @@
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M14" s="3">
         <v>14800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-5300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-8400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1579,8 +1618,14 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,35 +1639,35 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>100</v>
+      </c>
+      <c r="O15" s="3">
         <v>200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1698,8 +1743,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1789,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11800</v>
+        <v>8300</v>
       </c>
       <c r="E17" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11100</v>
+      </c>
+      <c r="G17" s="3">
         <v>16300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>14100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>17300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>16500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>13500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>-100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>16100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>19900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>8500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>9300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>14100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>13700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>14800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>8400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>8200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>10500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>10700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>16200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>19300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>31900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>13100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>14800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>9300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>8900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>9200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>10600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>3600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>4300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>3500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>8100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>1800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-11700</v>
+        <v>-8300</v>
       </c>
       <c r="E18" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-16300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-14100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-10100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-17100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-16500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-13500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-12600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-16100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-19900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>-14100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-13700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-14800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-8400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-8200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-31900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-14800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>-10600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-4300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-3500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-8100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,246 +2084,260 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-4100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>6300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>-900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>-900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15400</v>
+        <v>-6700</v>
       </c>
       <c r="E21" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="G21" s="3">
         <v>-18500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-9400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-6000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-20200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-15600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-11300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-4000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-9800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-15300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-20800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-13500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-12800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-15500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-6300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-8700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-8800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-17700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>-4400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO21" s="3" t="s">
+      <c r="AQ21" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2319,11 +2398,11 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
@@ -2331,11 +2410,11 @@
       <c r="Z22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2376,150 +2455,162 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-14400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-16900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-9000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-5300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-19500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-14800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-10400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-17600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-9000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-8900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-15200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-13700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-13000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-15600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-8800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>4</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>4</v>
@@ -2533,11 +2624,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2614,8 +2705,14 @@
       <c r="AO24" s="3">
         <v>0</v>
       </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2830,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-14400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-16900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-9000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-19500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-14800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-10400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-17600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-9000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-12000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-8900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-15200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-13700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-13000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-15600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-6500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-8800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-16900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-9000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-19500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-14800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-10400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-17600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-9000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-15200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-13700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-13000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-15600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-6500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-8800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3205,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3209,8 +3330,14 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3455,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,246 +3580,264 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>4100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>2100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>1000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>2400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-16900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-9000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-19500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-14800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-10400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-17600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-9000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-12000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-15200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-13700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-13000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-15600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-6500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-8800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3955,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-16900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-9000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-19500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-14800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-10400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-17600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-9000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-12000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-15200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-13700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-13000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-15600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-6500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-8800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4259,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,147 +4304,155 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F41" s="3">
         <v>7600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>51100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>29200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>20500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>27100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>14100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>23000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>21300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>18000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>19400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>16800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>34900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>14800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>12600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>11500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>46100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>6200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>5400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>63600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>7100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>26600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>62400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>171400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>126500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>138300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>24800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>28400</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM41" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN41" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO41" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ41" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>44500</v>
+        <v>28600</v>
       </c>
       <c r="E42" s="3">
+        <v>35700</v>
+      </c>
+      <c r="F42" s="3">
+        <v>44800</v>
+      </c>
+      <c r="G42" s="3">
         <v>41100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>20100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>35700</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -4282,74 +4461,74 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>5700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>72600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>88200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>92600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>63100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>75600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>88500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>123000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>137100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>79400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>52900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>103200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>115900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>32500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>27700</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="3">
         <v>49300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>38900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>60000</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH42" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AI42" s="3" t="s">
         <v>4</v>
       </c>
@@ -4359,11 +4538,11 @@
       <c r="AK42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="3">
-        <v>0</v>
+      <c r="AL42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN42" s="3">
         <v>0</v>
@@ -4371,77 +4550,83 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F43" s="3">
         <v>2300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>4</v>
       </c>
@@ -4454,11 +4639,11 @@
       <c r="AC43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF43" s="3">
         <v>0</v>
@@ -4490,47 +4675,53 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>6000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>7500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>7100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>10800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>10300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>11900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>12600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
@@ -4543,11 +4734,11 @@
       <c r="S44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -4609,246 +4800,264 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7900</v>
+        <v>5900</v>
       </c>
       <c r="E45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F45" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G45" s="3">
         <v>12300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6200</v>
       </c>
-      <c r="G45" s="3">
-        <v>45900</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J45" s="3">
         <v>38600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>63800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>68200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>89800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>104700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>90500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>74700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>15700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>8200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>11000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>13600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>11900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>5800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>4400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>6900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>3700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>3900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>3200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>100200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>136800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>104100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>126600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>121600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>1800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>9800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>1900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>1200</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM45" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO45" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ45" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F46" s="3">
         <v>74500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>77700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>92500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>74200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>82100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>97800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>111100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>121000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>135000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>122500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>83000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>107900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>117500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>122000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>112800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>103700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>108000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>139900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>153900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>86100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>103000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>110800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>121200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>138900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>169900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>167700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>183000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>187100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>124200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>181200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>127300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>139100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>26700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>29600</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM46" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN46" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO46" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ46" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4856,58 +5065,58 @@
         <v>300</v>
       </c>
       <c r="E47" s="3">
-        <v>7300</v>
+        <v>300</v>
       </c>
       <c r="F47" s="3">
         <v>300</v>
       </c>
       <c r="G47" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H47" s="3">
+        <v>300</v>
+      </c>
+      <c r="I47" s="3">
         <v>3200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>10000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>20700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>8700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>3200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>10100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>29500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>28800</v>
-      </c>
-      <c r="U47" s="3">
-        <v>300</v>
-      </c>
-      <c r="V47" s="3">
-        <v>300</v>
       </c>
       <c r="W47" s="3">
         <v>300</v>
@@ -4934,31 +5143,31 @@
         <v>300</v>
       </c>
       <c r="AE47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG47" s="3">
         <v>200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>57400</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>100</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
-      </c>
       <c r="AK47" s="3">
         <v>0</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM47" s="3" t="s">
-        <v>4</v>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3">
+        <v>0</v>
       </c>
       <c r="AN47" s="3" t="s">
         <v>4</v>
@@ -4966,127 +5175,139 @@
       <c r="AO47" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ47" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F48" s="3">
         <v>1500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1500</v>
       </c>
       <c r="M48" s="3">
         <v>1500</v>
       </c>
       <c r="N48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O48" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P48" s="3">
         <v>1700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>2000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>100</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM48" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN48" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO48" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ48" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5094,22 +5315,22 @@
         <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>100</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -5118,16 +5339,16 @@
         <v>100</v>
       </c>
       <c r="M49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>100</v>
       </c>
       <c r="O49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P49" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q49" s="3">
         <v>200</v>
@@ -5136,10 +5357,10 @@
         <v>200</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T49" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U49" s="3">
         <v>300</v>
@@ -5151,52 +5372,52 @@
         <v>300</v>
       </c>
       <c r="X49" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z49" s="3">
         <v>400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>500</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>600</v>
       </c>
       <c r="AC49" s="3">
         <v>500</v>
       </c>
       <c r="AD49" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF49" s="3">
         <v>400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>300</v>
       </c>
-      <c r="AF49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
         <v>100</v>
       </c>
-      <c r="AH49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
       <c r="AK49" s="3">
         <v>0</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM49" s="3" t="s">
-        <v>4</v>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="3">
+        <v>0</v>
       </c>
       <c r="AN49" s="3" t="s">
         <v>4</v>
@@ -5204,8 +5425,14 @@
       <c r="AO49" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ49" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5550,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,8 +5675,14 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5457,19 +5696,19 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
-        <v>300</v>
-      </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -5484,10 +5723,10 @@
         <v>300</v>
       </c>
       <c r="P52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q52" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
@@ -5511,37 +5750,37 @@
         <v>400</v>
       </c>
       <c r="Y52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z52" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA52" s="3">
         <v>500</v>
       </c>
       <c r="AB52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD52" s="3">
         <v>600</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>0</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>0</v>
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>4</v>
+      <c r="AI52" s="3">
+        <v>0</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>4</v>
@@ -5549,11 +5788,11 @@
       <c r="AK52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AL52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM52" s="3">
-        <v>0</v>
+      <c r="AL52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN52" s="3">
         <v>0</v>
@@ -5561,8 +5800,14 @@
       <c r="AO52" s="3">
         <v>0</v>
       </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5925,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>64800</v>
+      </c>
+      <c r="F54" s="3">
         <v>76400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>86300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>94000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>78700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>88900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>99700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>115500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>132900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>137100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>145200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>93800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>113400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>120100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>124700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>125200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>135700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>139300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>142900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>155800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>88000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>105200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>113300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>123800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>141900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>173400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>170500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>185400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>188300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>182300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>181800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>127600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>139400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>26900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>29800</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM54" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN54" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO54" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ54" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +6099,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,127 +6144,135 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>8600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>10300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>9300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>12400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>9400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>8200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>10400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>11600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>11400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>14500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>20300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>14300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>8400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>7900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>3400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>2800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>2800</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM57" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN57" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO57" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ57" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6013,13 +6280,13 @@
         <v>300</v>
       </c>
       <c r="E58" s="3">
+        <v>300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>400</v>
       </c>
       <c r="H58" s="3">
         <v>400</v>
@@ -6067,46 +6334,46 @@
         <v>400</v>
       </c>
       <c r="W58" s="3">
+        <v>400</v>
+      </c>
+      <c r="X58" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>500</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>600</v>
       </c>
       <c r="AA58" s="3">
         <v>600</v>
       </c>
       <c r="AB58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD58" s="3">
         <v>400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>300</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AG58" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -6123,308 +6390,326 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F59" s="3">
         <v>9400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3200</v>
       </c>
       <c r="L59" s="3">
         <v>3200</v>
       </c>
       <c r="M59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>8500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1000</v>
       </c>
       <c r="Y59" s="3">
         <v>1500</v>
       </c>
       <c r="Z59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB59" s="3">
         <v>800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>5100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>1700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>1200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>200</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN59" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO59" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ59" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F60" s="3">
         <v>22400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>17500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>14700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>15500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>11000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>12500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>11300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>14400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>12300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>20600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>20300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>14000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>10700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>8700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>11900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>13600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>12800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>16400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>21700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>15700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>10100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>9200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>6600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>4100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>4600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>3000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>3000</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM60" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN60" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO60" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ60" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>700</v>
+      </c>
+      <c r="E61" s="3">
         <v>800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
+        <v>800</v>
+      </c>
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>600</v>
-      </c>
-      <c r="J61" s="3">
-        <v>800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>800</v>
       </c>
       <c r="L61" s="3">
         <v>800</v>
       </c>
       <c r="M61" s="3">
+        <v>800</v>
+      </c>
+      <c r="N61" s="3">
+        <v>800</v>
+      </c>
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1400</v>
-      </c>
-      <c r="V61" s="3">
-        <v>200</v>
-      </c>
-      <c r="W61" s="3">
-        <v>300</v>
       </c>
       <c r="X61" s="3">
         <v>200</v>
@@ -6433,26 +6718,26 @@
         <v>300</v>
       </c>
       <c r="Z61" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC61" s="3">
         <v>400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>600</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -6463,25 +6748,31 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL61" s="3">
         <v>64400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>63500</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="3">
-        <v>0</v>
-      </c>
       <c r="AN61" s="3">
         <v>0</v>
       </c>
       <c r="AO61" s="3">
         <v>0</v>
       </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6518,35 +6809,35 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>4</v>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>4</v>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>4</v>
@@ -6554,14 +6845,14 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>100</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD62" s="3">
         <v>100</v>
@@ -6576,10 +6867,10 @@
         <v>100</v>
       </c>
       <c r="AH62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI62" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ62" s="3">
         <v>0</v>
@@ -6587,11 +6878,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM62" s="3" t="s">
-        <v>4</v>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="3">
+        <v>0</v>
       </c>
       <c r="AN62" s="3" t="s">
         <v>4</v>
@@ -6599,8 +6890,14 @@
       <c r="AO62" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ62" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +7015,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +7140,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7265,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F66" s="3">
         <v>23200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>19300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>15100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>19500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>12200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>9100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>8400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>21700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>21500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>15200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>8900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>10300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>12100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>13900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>13100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>16800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>22500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>16500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>10800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>9300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>6700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>4200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>4600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>67500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>66500</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM66" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN66" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO66" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ66" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7439,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7560,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7685,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7810,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7935,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-442100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-443600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-430800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-416800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-368000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-343900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-364800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-331800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-319100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-316300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-286000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-286800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-276600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-229100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-215300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-209200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-212000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-198800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-184400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-169600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-155000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-141700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-138500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-137500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-127100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-127500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-118500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-98800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-84400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-74300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>172100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>174200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>119900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>130800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-40200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-36300</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO72" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ72" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8185,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8310,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8435,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>48800</v>
+      </c>
+      <c r="F76" s="3">
         <v>53200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>67000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>76200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>63600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>72800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>88000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>102200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>113400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>124900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>136100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>85400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>97900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>107500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>111100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>103500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>114100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>124100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>130800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>146900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>77700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>93100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>99400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>110800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>125100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>150900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>154000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>174600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>179100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>175600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>177600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>123000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>134000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>-40600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>-36700</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM76" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AN76" s="3" t="s">
         <v>4</v>
       </c>
       <c r="AO76" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AP76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ76" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8685,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-12500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-16900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-9000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-19500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-14800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-10400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-17600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-9000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-12000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-15200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-13700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-13000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-15600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-6500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-8800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-15900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-29500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-2700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-11300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,8 +8989,10 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8609,28 +9006,28 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>200</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -8672,25 +9069,25 @@
         <v>200</v>
       </c>
       <c r="AB83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC83" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AD83" s="3">
         <v>100</v>
       </c>
       <c r="AE83" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AF83" s="3">
         <v>100</v>
       </c>
       <c r="AG83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI83" s="3">
         <v>0</v>
@@ -8710,11 +9107,17 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
-      <c r="AO83" s="3" t="s">
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ83" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9235,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9360,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9485,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9610,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9735,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-10600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-8900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-15100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-12300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-10800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-13000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-16000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-12000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-5600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-12200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-11400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-13600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-14000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-12700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-10700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-8300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-11000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-9700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-32000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-10000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-4200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-2800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>-5900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>-1500</v>
       </c>
-      <c r="AO89" s="3" t="s">
+      <c r="AQ89" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,20 +9909,22 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -9509,14 +9950,14 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -9536,61 +9977,67 @@
         <v>0</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-200</v>
       </c>
       <c r="AG91" s="3">
         <v>-300</v>
       </c>
       <c r="AH91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AI91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AJ91" s="3">
         <v>-100</v>
       </c>
       <c r="AK91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-100</v>
       </c>
-      <c r="AN91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO91" s="3" t="s">
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ91" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +10155,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10280,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F94" s="3">
         <v>3100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-29300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>19500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>6400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>29100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>7800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-26500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>5400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-15200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>28800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-36500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>6200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>3200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-7800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>33100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>27100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-24200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>19800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>7100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-107500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-9100</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AI94" s="3">
-        <v>-100</v>
       </c>
       <c r="AJ94" s="3">
         <v>-100</v>
       </c>
       <c r="AK94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AL94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-100</v>
       </c>
-      <c r="AN94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO94" s="3" t="s">
+      <c r="AP94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ94" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,8 +10454,10 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10027,11 +10494,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10108,8 +10575,14 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10700,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10825,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,8 +10950,14 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10474,19 +10965,19 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
         <v>29200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
@@ -10498,199 +10989,205 @@
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
         <v>58000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>2400</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-100</v>
       </c>
       <c r="R100" s="3">
         <v>-100</v>
       </c>
       <c r="S100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T100" s="3">
         <v>-100</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
-      </c>
-      <c r="V100" s="3">
-        <v>65400</v>
       </c>
       <c r="W100" s="3">
         <v>-100</v>
       </c>
       <c r="X100" s="3">
+        <v>65400</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z100" s="3">
         <v>9300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-100</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>54000</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>120400</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK100" s="3">
-        <v>0</v>
-      </c>
       <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="3">
         <v>1800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>36200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>36300</v>
       </c>
-      <c r="AO100" s="3" t="s">
+      <c r="AQ100" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>1400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>1200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>1800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>5800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
         <v>0</v>
       </c>
@@ -10700,126 +11197,138 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
-      <c r="AO101" s="3" t="s">
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-7700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-40300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>31200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>13300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-9900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-15400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-26900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>15100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-47400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-6700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>55800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-18800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>32600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>7100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-110400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>44800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-8800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>113500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-2800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>30300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>34700</v>
       </c>
-      <c r="AO102" s="3" t="s">
+      <c r="AQ102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
